--- a/public/data/‏‏Russian_Daily_Word.xlsx
+++ b/public/data/‏‏Russian_Daily_Word.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998D418B-08B1-4C5D-A292-90E1680562F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3F2BFD-0E9D-409D-846B-98B949732716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="2580" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/public/data/‏‏Russian_Daily_Word.xlsx
+++ b/public/data/‏‏Russian_Daily_Word.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3F2BFD-0E9D-409D-846B-98B949732716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ECB89C-1D42-495E-8200-1B038022D1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2580" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5869,7 +5869,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1726</v>
       </c>
       <c r="C1" s="4" t="s">

--- a/public/data/‏‏Russian_Daily_Word.xlsx
+++ b/public/data/‏‏Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ECB89C-1D42-495E-8200-1B038022D1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1979DBDC-0422-4503-A4AC-E83217C33052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5534,7 +5534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5551,6 +5551,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5869,7 +5870,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1726</v>
       </c>
       <c r="C1" s="4" t="s">

--- a/public/data/‏‏Russian_Daily_Word.xlsx
+++ b/public/data/‏‏Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1979DBDC-0422-4503-A4AC-E83217C33052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D65433-CEF9-4233-B486-5ED5592096C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5534,24 +5534,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5859,33 +5852,33 @@
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="84.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="84.58203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>1726</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1469</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>1468</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>1471</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>1467</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>1466</v>
       </c>
     </row>
@@ -5896,19 +5889,19 @@
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>1472</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5919,19 +5912,19 @@
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>1473</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5942,19 +5935,19 @@
       <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>1474</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>1470</v>
       </c>
     </row>
@@ -5965,19 +5958,19 @@
       <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>1475</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5988,19 +5981,19 @@
       <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>1476</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6011,19 +6004,19 @@
       <c r="B7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>1477</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6034,19 +6027,19 @@
       <c r="B8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>1478</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -6057,19 +6050,19 @@
       <c r="B9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>1479</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -6080,19 +6073,19 @@
       <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>1480</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6103,19 +6096,19 @@
       <c r="B11" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>1481</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6126,19 +6119,19 @@
       <c r="B12" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>1482</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6149,19 +6142,19 @@
       <c r="B13" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -6172,19 +6165,19 @@
       <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>1484</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -6195,19 +6188,19 @@
       <c r="B15" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -6218,19 +6211,19 @@
       <c r="B16" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -6241,19 +6234,19 @@
       <c r="B17" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>93</v>
       </c>
     </row>
@@ -6264,19 +6257,19 @@
       <c r="B18" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>1488</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -6287,19 +6280,19 @@
       <c r="B19" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>1489</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -6310,19 +6303,19 @@
       <c r="B20" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>1490</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>108</v>
       </c>
     </row>
@@ -6333,19 +6326,19 @@
       <c r="B21" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>1491</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>113</v>
       </c>
     </row>
@@ -6356,19 +6349,19 @@
       <c r="B22" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>1509</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>118</v>
       </c>
     </row>
@@ -6379,19 +6372,19 @@
       <c r="B23" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>123</v>
       </c>
     </row>
@@ -6402,19 +6395,19 @@
       <c r="B24" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>1493</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>128</v>
       </c>
     </row>
@@ -6425,19 +6418,19 @@
       <c r="B25" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>1494</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>133</v>
       </c>
     </row>
@@ -6448,19 +6441,19 @@
       <c r="B26" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>1495</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -6471,19 +6464,19 @@
       <c r="B27" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>143</v>
       </c>
     </row>
@@ -6494,19 +6487,19 @@
       <c r="B28" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>1496</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6517,19 +6510,19 @@
       <c r="B29" t="s">
         <v>149</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>153</v>
       </c>
     </row>
@@ -6540,19 +6533,19 @@
       <c r="B30" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>1498</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>158</v>
       </c>
     </row>
@@ -6563,19 +6556,19 @@
       <c r="B31" t="s">
         <v>159</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>1499</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -6586,19 +6579,19 @@
       <c r="B32" t="s">
         <v>164</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="2" t="s">
         <v>1500</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6609,19 +6602,19 @@
       <c r="B33" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>1501</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -6632,19 +6625,19 @@
       <c r="B34" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="2" t="s">
         <v>1502</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="1" t="s">
         <v>178</v>
       </c>
     </row>
@@ -6655,19 +6648,19 @@
       <c r="B35" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="2" t="s">
         <v>1503</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>183</v>
       </c>
     </row>
@@ -6678,19 +6671,19 @@
       <c r="B36" t="s">
         <v>184</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>1504</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="1" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6701,19 +6694,19 @@
       <c r="B37" t="s">
         <v>189</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>1505</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>192</v>
       </c>
     </row>
@@ -6724,19 +6717,19 @@
       <c r="B38" t="s">
         <v>193</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="2" t="s">
         <v>1506</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="1" t="s">
         <v>197</v>
       </c>
     </row>
@@ -6747,19 +6740,19 @@
       <c r="B39" t="s">
         <v>198</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="2" t="s">
         <v>1507</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6770,19 +6763,19 @@
       <c r="B40" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="2" t="s">
         <v>1508</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="1" t="s">
         <v>206</v>
       </c>
     </row>
@@ -6793,19 +6786,19 @@
       <c r="B41" t="s">
         <v>207</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="2" t="s">
         <v>1510</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>211</v>
       </c>
     </row>
@@ -6816,19 +6809,19 @@
       <c r="B42" t="s">
         <v>212</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="2" t="s">
         <v>1511</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="1" t="s">
         <v>216</v>
       </c>
     </row>
@@ -6839,19 +6832,19 @@
       <c r="B43" t="s">
         <v>217</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="2" t="s">
         <v>1512</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="1" t="s">
         <v>221</v>
       </c>
     </row>
@@ -6862,19 +6855,19 @@
       <c r="B44" t="s">
         <v>222</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="2" t="s">
         <v>1513</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="1" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6885,19 +6878,19 @@
       <c r="B45" t="s">
         <v>227</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="2" t="s">
         <v>1514</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -6908,19 +6901,19 @@
       <c r="B46" t="s">
         <v>232</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="2" t="s">
         <v>1526</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="1" t="s">
         <v>236</v>
       </c>
     </row>
@@ -6931,19 +6924,19 @@
       <c r="B47" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="2" t="s">
         <v>1515</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="1" t="s">
         <v>241</v>
       </c>
     </row>
@@ -6954,19 +6947,19 @@
       <c r="B48" t="s">
         <v>242</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="2" t="s">
         <v>1527</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="1" t="s">
         <v>246</v>
       </c>
     </row>
@@ -6977,19 +6970,19 @@
       <c r="B49" t="s">
         <v>247</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="2" t="s">
         <v>1516</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="1" t="s">
         <v>251</v>
       </c>
     </row>
@@ -7000,19 +6993,19 @@
       <c r="B50" t="s">
         <v>252</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="2" t="s">
         <v>1517</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="1" t="s">
         <v>256</v>
       </c>
     </row>
@@ -7023,19 +7016,19 @@
       <c r="B51" t="s">
         <v>257</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="2" t="s">
         <v>1518</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="1" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7046,19 +7039,19 @@
       <c r="B52" t="s">
         <v>262</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="2" t="s">
         <v>1519</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="1" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7069,19 +7062,19 @@
       <c r="B53" t="s">
         <v>267</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="2" t="s">
         <v>1520</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="1" t="s">
         <v>271</v>
       </c>
     </row>
@@ -7092,19 +7085,19 @@
       <c r="B54" t="s">
         <v>272</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="1" t="s">
         <v>276</v>
       </c>
     </row>
@@ -7115,19 +7108,19 @@
       <c r="B55" t="s">
         <v>277</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="2" t="s">
         <v>1528</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -7138,19 +7131,19 @@
       <c r="B56" t="s">
         <v>282</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="2" t="s">
         <v>1529</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="1" t="s">
         <v>286</v>
       </c>
     </row>
@@ -7161,19 +7154,19 @@
       <c r="B57" t="s">
         <v>287</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="2" t="s">
         <v>1521</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="1" t="s">
         <v>291</v>
       </c>
     </row>
@@ -7184,19 +7177,19 @@
       <c r="B58" t="s">
         <v>292</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="2" t="s">
         <v>1522</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="1" t="s">
         <v>296</v>
       </c>
     </row>
@@ -7207,19 +7200,19 @@
       <c r="B59" t="s">
         <v>297</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="2" t="s">
         <v>1523</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="1" t="s">
         <v>301</v>
       </c>
     </row>
@@ -7230,19 +7223,19 @@
       <c r="B60" t="s">
         <v>302</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="1" t="s">
         <v>306</v>
       </c>
     </row>
@@ -7253,19 +7246,19 @@
       <c r="B61" t="s">
         <v>307</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="2" t="s">
         <v>1525</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="1" t="s">
         <v>311</v>
       </c>
     </row>
@@ -7276,19 +7269,19 @@
       <c r="B62" t="s">
         <v>312</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="2" t="s">
         <v>1530</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="1" t="s">
         <v>316</v>
       </c>
     </row>
@@ -7299,19 +7292,19 @@
       <c r="B63" t="s">
         <v>317</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="2" t="s">
         <v>1531</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="1" t="s">
         <v>321</v>
       </c>
     </row>
@@ -7322,19 +7315,19 @@
       <c r="B64" t="s">
         <v>322</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="2" t="s">
         <v>1531</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="1" t="s">
         <v>325</v>
       </c>
     </row>
@@ -7345,19 +7338,19 @@
       <c r="B65" t="s">
         <v>326</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="2" t="s">
         <v>1532</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="1" t="s">
         <v>329</v>
       </c>
     </row>
@@ -7368,19 +7361,19 @@
       <c r="B66" t="s">
         <v>330</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="2" t="s">
         <v>1533</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="1" t="s">
         <v>334</v>
       </c>
     </row>
@@ -7391,19 +7384,19 @@
       <c r="B67" t="s">
         <v>335</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="2" t="s">
         <v>1553</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="1" t="s">
         <v>339</v>
       </c>
     </row>
@@ -7414,19 +7407,19 @@
       <c r="B68" t="s">
         <v>340</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="2" t="s">
         <v>1534</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="G68" s="1" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7437,19 +7430,19 @@
       <c r="B69" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="2" t="s">
         <v>1525</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="1" t="s">
         <v>349</v>
       </c>
     </row>
@@ -7460,19 +7453,19 @@
       <c r="B70" t="s">
         <v>350</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="1" t="s">
         <v>354</v>
       </c>
     </row>
@@ -7483,19 +7476,19 @@
       <c r="B71" t="s">
         <v>355</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="2" t="s">
         <v>1535</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="1" t="s">
         <v>359</v>
       </c>
     </row>
@@ -7506,19 +7499,19 @@
       <c r="B72" t="s">
         <v>360</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D72" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="2" t="s">
         <v>1554</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" s="1" t="s">
         <v>364</v>
       </c>
     </row>
@@ -7529,19 +7522,19 @@
       <c r="B73" t="s">
         <v>365</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D73" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="2" t="s">
         <v>1536</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="1" t="s">
         <v>369</v>
       </c>
     </row>
@@ -7552,19 +7545,19 @@
       <c r="B74" t="s">
         <v>370</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="2" t="s">
         <v>1537</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" s="1" t="s">
         <v>374</v>
       </c>
     </row>
@@ -7575,19 +7568,19 @@
       <c r="B75" t="s">
         <v>375</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="2" t="s">
         <v>1538</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="1" t="s">
         <v>379</v>
       </c>
     </row>
@@ -7598,19 +7591,19 @@
       <c r="B76" t="s">
         <v>380</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="2" t="s">
         <v>1539</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="1" t="s">
         <v>384</v>
       </c>
     </row>
@@ -7621,19 +7614,19 @@
       <c r="B77" t="s">
         <v>385</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="2" t="s">
         <v>1540</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="1" t="s">
         <v>389</v>
       </c>
     </row>
@@ -7644,19 +7637,19 @@
       <c r="B78" t="s">
         <v>390</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="2" t="s">
         <v>1541</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="1" t="s">
         <v>394</v>
       </c>
     </row>
@@ -7667,19 +7660,19 @@
       <c r="B79" t="s">
         <v>395</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="D79" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="2" t="s">
         <v>1523</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="1" t="s">
         <v>399</v>
       </c>
     </row>
@@ -7690,19 +7683,19 @@
       <c r="B80" t="s">
         <v>400</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="2" t="s">
         <v>1542</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="1" t="s">
         <v>404</v>
       </c>
     </row>
@@ -7713,19 +7706,19 @@
       <c r="B81" t="s">
         <v>405</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="2" t="s">
         <v>1543</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" s="1" t="s">
         <v>409</v>
       </c>
     </row>
@@ -7736,19 +7729,19 @@
       <c r="B82" t="s">
         <v>410</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="2" t="s">
         <v>1544</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="1" t="s">
         <v>414</v>
       </c>
     </row>
@@ -7759,19 +7752,19 @@
       <c r="B83" t="s">
         <v>415</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="2" t="s">
         <v>1521</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" s="1" t="s">
         <v>419</v>
       </c>
     </row>
@@ -7782,19 +7775,19 @@
       <c r="B84" t="s">
         <v>420</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="1" t="s">
         <v>424</v>
       </c>
     </row>
@@ -7805,19 +7798,19 @@
       <c r="B85" t="s">
         <v>425</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="2" t="s">
         <v>1545</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" s="1" t="s">
         <v>428</v>
       </c>
     </row>
@@ -7828,19 +7821,19 @@
       <c r="B86" t="s">
         <v>429</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="2" t="s">
         <v>1546</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="1" t="s">
         <v>433</v>
       </c>
     </row>
@@ -7851,19 +7844,19 @@
       <c r="B87" t="s">
         <v>434</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="2" t="s">
         <v>1547</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="1" t="s">
         <v>438</v>
       </c>
     </row>
@@ -7874,19 +7867,19 @@
       <c r="B88" t="s">
         <v>439</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="2" t="s">
         <v>1548</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="1" t="s">
         <v>443</v>
       </c>
     </row>
@@ -7897,19 +7890,19 @@
       <c r="B89" t="s">
         <v>444</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="2" t="s">
         <v>1549</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="1" t="s">
         <v>448</v>
       </c>
     </row>
@@ -7920,19 +7913,19 @@
       <c r="B90" t="s">
         <v>449</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="2" t="s">
         <v>1550</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G90" s="1" t="s">
         <v>453</v>
       </c>
     </row>
@@ -7943,19 +7936,19 @@
       <c r="B91" t="s">
         <v>454</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="2" t="s">
         <v>1551</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="1" t="s">
         <v>458</v>
       </c>
     </row>
@@ -7966,19 +7959,19 @@
       <c r="B92" t="s">
         <v>459</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="2" t="s">
         <v>1551</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="1" t="s">
         <v>463</v>
       </c>
     </row>
@@ -7989,19 +7982,19 @@
       <c r="B93" t="s">
         <v>464</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="2" t="s">
         <v>1551</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G93" s="1" t="s">
         <v>468</v>
       </c>
     </row>
@@ -8012,19 +8005,19 @@
       <c r="B94" t="s">
         <v>469</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="1" t="s">
         <v>471</v>
       </c>
       <c r="E94" t="s">
         <v>1555</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G94" s="1" t="s">
         <v>473</v>
       </c>
     </row>
@@ -8035,19 +8028,19 @@
       <c r="B95" t="s">
         <v>474</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="1" t="s">
         <v>476</v>
       </c>
       <c r="E95" t="s">
         <v>1550</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="1" t="s">
         <v>478</v>
       </c>
     </row>
@@ -8058,19 +8051,19 @@
       <c r="B96" t="s">
         <v>479</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="1" t="s">
         <v>481</v>
       </c>
       <c r="E96" t="s">
         <v>1556</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G96" s="1" t="s">
         <v>483</v>
       </c>
     </row>
@@ -8081,19 +8074,19 @@
       <c r="B97" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="1" t="s">
         <v>486</v>
       </c>
       <c r="E97" t="s">
         <v>1557</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="G97" s="1" t="s">
         <v>488</v>
       </c>
     </row>
@@ -8104,19 +8097,19 @@
       <c r="B98" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="1" t="s">
         <v>491</v>
       </c>
       <c r="E98" t="s">
         <v>1558</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="1" t="s">
         <v>493</v>
       </c>
     </row>
@@ -8127,19 +8120,19 @@
       <c r="B99" t="s">
         <v>494</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="1" t="s">
         <v>496</v>
       </c>
       <c r="E99" t="s">
         <v>1559</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G99" s="1" t="s">
         <v>498</v>
       </c>
     </row>
@@ -8150,19 +8143,19 @@
       <c r="B100" t="s">
         <v>499</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="1" t="s">
         <v>501</v>
       </c>
       <c r="E100" t="s">
         <v>1560</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="G100" s="1" t="s">
         <v>503</v>
       </c>
     </row>
@@ -8173,19 +8166,19 @@
       <c r="B101" t="s">
         <v>504</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D101" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E101" t="s">
         <v>1561</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="G101" s="1" t="s">
         <v>508</v>
       </c>
     </row>
@@ -8196,19 +8189,19 @@
       <c r="B102" t="s">
         <v>509</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="1" t="s">
         <v>511</v>
       </c>
       <c r="E102" t="s">
         <v>1562</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="G102" s="1" t="s">
         <v>513</v>
       </c>
     </row>
@@ -8219,19 +8212,19 @@
       <c r="B103" t="s">
         <v>514</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" s="1" t="s">
         <v>516</v>
       </c>
       <c r="E103" t="s">
         <v>1563</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="G103" s="1" t="s">
         <v>518</v>
       </c>
     </row>
@@ -8242,19 +8235,19 @@
       <c r="B104" t="s">
         <v>519</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="1" t="s">
         <v>521</v>
       </c>
       <c r="E104" t="s">
         <v>1564</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="G104" s="1" t="s">
         <v>523</v>
       </c>
     </row>
@@ -8265,19 +8258,19 @@
       <c r="B105" t="s">
         <v>524</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="D105" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E105" t="s">
         <v>1565</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="G105" s="1" t="s">
         <v>528</v>
       </c>
     </row>
@@ -8288,19 +8281,19 @@
       <c r="B106" t="s">
         <v>529</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E106" t="s">
         <v>1566</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="G106" s="1" t="s">
         <v>533</v>
       </c>
     </row>
@@ -8311,19 +8304,19 @@
       <c r="B107" t="s">
         <v>534</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="1" t="s">
         <v>536</v>
       </c>
       <c r="E107" t="s">
         <v>1567</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="G107" s="1" t="s">
         <v>538</v>
       </c>
     </row>
@@ -8334,19 +8327,19 @@
       <c r="B108" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D108" s="1" t="s">
         <v>541</v>
       </c>
       <c r="E108" t="s">
         <v>1568</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="G108" s="1" t="s">
         <v>543</v>
       </c>
     </row>
@@ -8357,19 +8350,19 @@
       <c r="B109" t="s">
         <v>544</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="1" t="s">
         <v>546</v>
       </c>
       <c r="E109" t="s">
         <v>1569</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="G109" s="1" t="s">
         <v>548</v>
       </c>
     </row>
@@ -8380,19 +8373,19 @@
       <c r="B110" t="s">
         <v>549</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="1" t="s">
         <v>551</v>
       </c>
       <c r="E110" t="s">
         <v>1570</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="G110" s="1" t="s">
         <v>553</v>
       </c>
     </row>
@@ -8403,19 +8396,19 @@
       <c r="B111" t="s">
         <v>554</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="1" t="s">
         <v>556</v>
       </c>
       <c r="E111" t="s">
         <v>1571</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="G111" s="1" t="s">
         <v>557</v>
       </c>
     </row>
@@ -8426,19 +8419,19 @@
       <c r="B112" t="s">
         <v>558</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="1" t="s">
         <v>560</v>
       </c>
       <c r="E112" t="s">
         <v>1572</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G112" s="1" t="s">
         <v>562</v>
       </c>
     </row>
@@ -8449,19 +8442,19 @@
       <c r="B113" t="s">
         <v>563</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D113" s="1" t="s">
         <v>565</v>
       </c>
       <c r="E113" t="s">
         <v>1573</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="G113" s="1" t="s">
         <v>567</v>
       </c>
     </row>
@@ -8472,19 +8465,19 @@
       <c r="B114" t="s">
         <v>568</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D114" s="1" t="s">
         <v>570</v>
       </c>
       <c r="E114" t="s">
         <v>1574</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="G114" s="2" t="s">
+      <c r="G114" s="1" t="s">
         <v>572</v>
       </c>
     </row>
@@ -8495,19 +8488,19 @@
       <c r="B115" t="s">
         <v>573</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D115" s="1" t="s">
         <v>575</v>
       </c>
       <c r="E115" t="s">
         <v>1575</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="G115" s="1" t="s">
         <v>576</v>
       </c>
     </row>
@@ -8518,19 +8511,19 @@
       <c r="B116" t="s">
         <v>577</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D116" s="1" t="s">
         <v>579</v>
       </c>
       <c r="E116" t="s">
         <v>1576</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="G116" s="1" t="s">
         <v>581</v>
       </c>
     </row>
@@ -8541,19 +8534,19 @@
       <c r="B117" t="s">
         <v>582</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" s="1" t="s">
         <v>584</v>
       </c>
       <c r="E117" t="s">
         <v>1577</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="G117" s="2" t="s">
+      <c r="G117" s="1" t="s">
         <v>585</v>
       </c>
     </row>
@@ -8564,19 +8557,19 @@
       <c r="B118" t="s">
         <v>586</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="1" t="s">
         <v>588</v>
       </c>
       <c r="E118" t="s">
         <v>1521</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G118" s="1" t="s">
         <v>590</v>
       </c>
     </row>
@@ -8587,19 +8580,19 @@
       <c r="B119" t="s">
         <v>591</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D119" s="1" t="s">
         <v>593</v>
       </c>
       <c r="E119" t="s">
         <v>1578</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="G119" s="1" t="s">
         <v>595</v>
       </c>
     </row>
@@ -8610,19 +8603,19 @@
       <c r="B120" t="s">
         <v>596</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="D120" s="1" t="s">
         <v>598</v>
       </c>
       <c r="E120" t="s">
         <v>1579</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="G120" s="1" t="s">
         <v>599</v>
       </c>
     </row>
@@ -8633,19 +8626,19 @@
       <c r="B121" t="s">
         <v>600</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="1" t="s">
         <v>602</v>
       </c>
       <c r="E121" t="s">
         <v>1580</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="G121" s="1" t="s">
         <v>604</v>
       </c>
     </row>
@@ -8656,19 +8649,19 @@
       <c r="B122" t="s">
         <v>605</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D122" s="1" t="s">
         <v>607</v>
       </c>
       <c r="E122" t="s">
         <v>1581</v>
       </c>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="G122" s="2" t="s">
+      <c r="G122" s="1" t="s">
         <v>609</v>
       </c>
     </row>
@@ -8679,19 +8672,19 @@
       <c r="B123" t="s">
         <v>610</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D123" s="1" t="s">
         <v>612</v>
       </c>
       <c r="E123" t="s">
         <v>1582</v>
       </c>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G123" s="2" t="s">
+      <c r="G123" s="1" t="s">
         <v>614</v>
       </c>
     </row>
@@ -8702,19 +8695,19 @@
       <c r="B124" t="s">
         <v>615</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D124" s="1" t="s">
         <v>617</v>
       </c>
       <c r="E124" t="s">
         <v>1583</v>
       </c>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="G124" s="1" t="s">
         <v>619</v>
       </c>
     </row>
@@ -8725,19 +8718,19 @@
       <c r="B125" t="s">
         <v>620</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="D125" s="1" t="s">
         <v>622</v>
       </c>
       <c r="E125" t="s">
         <v>1584</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G125" s="2" t="s">
+      <c r="G125" s="1" t="s">
         <v>623</v>
       </c>
     </row>
@@ -8748,19 +8741,19 @@
       <c r="B126" t="s">
         <v>624</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="1" t="s">
         <v>626</v>
       </c>
       <c r="E126" t="s">
         <v>1585</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="G126" s="2" t="s">
+      <c r="G126" s="1" t="s">
         <v>628</v>
       </c>
     </row>
@@ -8771,19 +8764,19 @@
       <c r="B127" t="s">
         <v>629</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="1" t="s">
         <v>631</v>
       </c>
       <c r="E127" t="s">
         <v>1523</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="G127" s="1" t="s">
         <v>633</v>
       </c>
     </row>
@@ -8794,19 +8787,19 @@
       <c r="B128" t="s">
         <v>634</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D128" s="1" t="s">
         <v>636</v>
       </c>
       <c r="E128" t="s">
         <v>1586</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="G128" s="2" t="s">
+      <c r="G128" s="1" t="s">
         <v>638</v>
       </c>
     </row>
@@ -8817,19 +8810,19 @@
       <c r="B129" t="s">
         <v>639</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="D129" s="1" t="s">
         <v>641</v>
       </c>
       <c r="E129" t="s">
         <v>1587</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="G129" s="1" t="s">
         <v>643</v>
       </c>
     </row>
@@ -8840,19 +8833,19 @@
       <c r="B130" t="s">
         <v>644</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="D130" s="1" t="s">
         <v>646</v>
       </c>
       <c r="E130" t="s">
         <v>1562</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="G130" s="2" t="s">
+      <c r="G130" s="1" t="s">
         <v>648</v>
       </c>
     </row>
@@ -8863,19 +8856,19 @@
       <c r="B131" t="s">
         <v>649</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D131" s="1" t="s">
         <v>651</v>
       </c>
       <c r="E131" t="s">
         <v>1588</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="G131" s="2" t="s">
+      <c r="G131" s="1" t="s">
         <v>653</v>
       </c>
     </row>
@@ -8886,19 +8879,19 @@
       <c r="B132" t="s">
         <v>654</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="1" t="s">
         <v>656</v>
       </c>
       <c r="E132" t="s">
         <v>1589</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="G132" s="2" t="s">
+      <c r="G132" s="1" t="s">
         <v>657</v>
       </c>
     </row>
@@ -8909,19 +8902,19 @@
       <c r="B133" t="s">
         <v>658</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="1" t="s">
         <v>660</v>
       </c>
       <c r="E133" t="s">
         <v>1590</v>
       </c>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="G133" s="1" t="s">
         <v>662</v>
       </c>
     </row>
@@ -8932,19 +8925,19 @@
       <c r="B134" t="s">
         <v>663</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D134" s="1" t="s">
         <v>665</v>
       </c>
       <c r="E134" t="s">
         <v>1591</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="F134" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="G134" s="1" t="s">
         <v>667</v>
       </c>
     </row>
@@ -8955,19 +8948,19 @@
       <c r="B135" t="s">
         <v>668</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="1" t="s">
         <v>670</v>
       </c>
       <c r="E135" t="s">
         <v>1587</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F135" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="G135" s="2" t="s">
+      <c r="G135" s="1" t="s">
         <v>672</v>
       </c>
     </row>
@@ -8978,19 +8971,19 @@
       <c r="B136" t="s">
         <v>673</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D136" s="1" t="s">
         <v>675</v>
       </c>
       <c r="E136" t="s">
         <v>1592</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="F136" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="G136" s="1" t="s">
         <v>677</v>
       </c>
     </row>
@@ -9001,19 +8994,19 @@
       <c r="B137" t="s">
         <v>678</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="D137" s="1" t="s">
         <v>680</v>
       </c>
       <c r="E137" t="s">
         <v>1544</v>
       </c>
-      <c r="F137" s="3" t="s">
+      <c r="F137" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="G137" s="2" t="s">
+      <c r="G137" s="1" t="s">
         <v>682</v>
       </c>
     </row>
@@ -9024,19 +9017,19 @@
       <c r="B138" t="s">
         <v>683</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="D138" s="1" t="s">
         <v>685</v>
       </c>
       <c r="E138" t="s">
         <v>1593</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="F138" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="G138" s="2" t="s">
+      <c r="G138" s="1" t="s">
         <v>687</v>
       </c>
     </row>
@@ -9047,19 +9040,19 @@
       <c r="B139" t="s">
         <v>688</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="D139" s="1" t="s">
         <v>690</v>
       </c>
       <c r="E139" t="s">
         <v>1567</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="G139" s="2" t="s">
+      <c r="G139" s="1" t="s">
         <v>692</v>
       </c>
     </row>
@@ -9070,19 +9063,19 @@
       <c r="B140" t="s">
         <v>693</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D140" s="1" t="s">
         <v>695</v>
       </c>
       <c r="E140" t="s">
         <v>1594</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="F140" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="G140" s="1" t="s">
         <v>697</v>
       </c>
     </row>
@@ -9093,19 +9086,19 @@
       <c r="B141" t="s">
         <v>698</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="D141" s="1" t="s">
         <v>700</v>
       </c>
       <c r="E141" t="s">
         <v>1595</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="F141" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="G141" s="2" t="s">
+      <c r="G141" s="1" t="s">
         <v>702</v>
       </c>
     </row>
@@ -9116,19 +9109,19 @@
       <c r="B142" t="s">
         <v>703</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="D142" s="1" t="s">
         <v>705</v>
       </c>
       <c r="E142" t="s">
         <v>1596</v>
       </c>
-      <c r="F142" s="3" t="s">
+      <c r="F142" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="G142" s="2" t="s">
+      <c r="G142" s="1" t="s">
         <v>707</v>
       </c>
     </row>
@@ -9139,19 +9132,19 @@
       <c r="B143" t="s">
         <v>708</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="D143" s="1" t="s">
         <v>710</v>
       </c>
       <c r="E143" t="s">
         <v>1556</v>
       </c>
-      <c r="F143" s="3" t="s">
+      <c r="F143" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="G143" s="2" t="s">
+      <c r="G143" s="1" t="s">
         <v>712</v>
       </c>
     </row>
@@ -9162,19 +9155,19 @@
       <c r="B144" t="s">
         <v>713</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D144" s="1" t="s">
         <v>715</v>
       </c>
       <c r="E144" t="s">
         <v>1597</v>
       </c>
-      <c r="F144" s="3" t="s">
+      <c r="F144" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="G144" s="2" t="s">
+      <c r="G144" s="1" t="s">
         <v>717</v>
       </c>
     </row>
@@ -9185,19 +9178,19 @@
       <c r="B145" t="s">
         <v>718</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D145" s="1" t="s">
         <v>720</v>
       </c>
       <c r="E145" t="s">
         <v>1598</v>
       </c>
-      <c r="F145" s="3" t="s">
+      <c r="F145" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="G145" s="1" t="s">
         <v>722</v>
       </c>
     </row>
@@ -9208,19 +9201,19 @@
       <c r="B146" t="s">
         <v>723</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D146" s="1" t="s">
         <v>725</v>
       </c>
       <c r="E146" t="s">
         <v>1599</v>
       </c>
-      <c r="F146" s="3" t="s">
+      <c r="F146" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="G146" s="2" t="s">
+      <c r="G146" s="1" t="s">
         <v>727</v>
       </c>
     </row>
@@ -9231,19 +9224,19 @@
       <c r="B147" t="s">
         <v>728</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D147" s="1" t="s">
         <v>730</v>
       </c>
       <c r="E147" t="s">
         <v>1600</v>
       </c>
-      <c r="F147" s="3" t="s">
+      <c r="F147" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="G147" s="1" t="s">
         <v>732</v>
       </c>
     </row>
@@ -9254,19 +9247,19 @@
       <c r="B148" t="s">
         <v>733</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D148" s="1" t="s">
         <v>735</v>
       </c>
       <c r="E148" t="s">
         <v>1601</v>
       </c>
-      <c r="F148" s="3" t="s">
+      <c r="F148" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="G148" s="1" t="s">
         <v>737</v>
       </c>
     </row>
@@ -9277,19 +9270,19 @@
       <c r="B149" t="s">
         <v>738</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="D149" s="1" t="s">
         <v>740</v>
       </c>
       <c r="E149" t="s">
         <v>1602</v>
       </c>
-      <c r="F149" s="3" t="s">
+      <c r="F149" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="G149" s="2" t="s">
+      <c r="G149" s="1" t="s">
         <v>742</v>
       </c>
     </row>
@@ -9300,19 +9293,19 @@
       <c r="B150" t="s">
         <v>743</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D150" s="2" t="s">
+      <c r="D150" s="1" t="s">
         <v>300</v>
       </c>
       <c r="E150" t="s">
         <v>1602</v>
       </c>
-      <c r="F150" s="3" t="s">
+      <c r="F150" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="G150" s="2" t="s">
+      <c r="G150" s="1" t="s">
         <v>746</v>
       </c>
     </row>
@@ -9323,19 +9316,19 @@
       <c r="B151" t="s">
         <v>747</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="D151" s="1" t="s">
         <v>749</v>
       </c>
       <c r="E151" t="s">
         <v>1602</v>
       </c>
-      <c r="F151" s="3" t="s">
+      <c r="F151" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G151" s="2" t="s">
+      <c r="G151" s="1" t="s">
         <v>750</v>
       </c>
     </row>
@@ -9346,19 +9339,19 @@
       <c r="B152" t="s">
         <v>751</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D152" s="1" t="s">
         <v>753</v>
       </c>
       <c r="E152" t="s">
         <v>1602</v>
       </c>
-      <c r="F152" s="3" t="s">
+      <c r="F152" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="G152" s="1" t="s">
         <v>755</v>
       </c>
     </row>
@@ -9369,19 +9362,19 @@
       <c r="B153" t="s">
         <v>756</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="D153" s="1" t="s">
         <v>758</v>
       </c>
       <c r="E153" t="s">
         <v>1603</v>
       </c>
-      <c r="F153" s="3" t="s">
+      <c r="F153" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="G153" s="1" t="s">
         <v>760</v>
       </c>
     </row>
@@ -9392,19 +9385,19 @@
       <c r="B154" t="s">
         <v>761</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D154" s="1" t="s">
         <v>763</v>
       </c>
       <c r="E154" t="s">
         <v>1604</v>
       </c>
-      <c r="F154" s="3" t="s">
+      <c r="F154" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="G154" s="1" t="s">
         <v>765</v>
       </c>
     </row>
@@ -9415,19 +9408,19 @@
       <c r="B155" t="s">
         <v>766</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="D155" s="1" t="s">
         <v>768</v>
       </c>
       <c r="E155" t="s">
         <v>1618</v>
       </c>
-      <c r="F155" s="3" t="s">
+      <c r="F155" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="G155" s="1" t="s">
         <v>770</v>
       </c>
     </row>
@@ -9438,19 +9431,19 @@
       <c r="B156" t="s">
         <v>771</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="D156" s="1" t="s">
         <v>773</v>
       </c>
       <c r="E156" t="s">
         <v>1605</v>
       </c>
-      <c r="F156" s="3" t="s">
+      <c r="F156" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G156" s="1" t="s">
         <v>775</v>
       </c>
     </row>
@@ -9461,19 +9454,19 @@
       <c r="B157" t="s">
         <v>776</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="D157" s="1" t="s">
         <v>778</v>
       </c>
       <c r="E157" t="s">
         <v>1606</v>
       </c>
-      <c r="F157" s="3" t="s">
+      <c r="F157" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="G157" s="1" t="s">
         <v>780</v>
       </c>
     </row>
@@ -9484,19 +9477,19 @@
       <c r="B158" t="s">
         <v>781</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D158" s="1" t="s">
         <v>783</v>
       </c>
       <c r="E158" t="s">
         <v>1607</v>
       </c>
-      <c r="F158" s="3" t="s">
+      <c r="F158" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="G158" s="2" t="s">
+      <c r="G158" s="1" t="s">
         <v>785</v>
       </c>
     </row>
@@ -9507,19 +9500,19 @@
       <c r="B159" t="s">
         <v>786</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D159" s="1" t="s">
         <v>788</v>
       </c>
       <c r="E159" t="s">
         <v>1608</v>
       </c>
-      <c r="F159" s="3" t="s">
+      <c r="F159" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="G159" s="2" t="s">
+      <c r="G159" s="1" t="s">
         <v>790</v>
       </c>
     </row>
@@ -9530,19 +9523,19 @@
       <c r="B160" t="s">
         <v>791</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="D160" s="2" t="s">
+      <c r="D160" s="1" t="s">
         <v>793</v>
       </c>
       <c r="E160" t="s">
         <v>1609</v>
       </c>
-      <c r="F160" s="3" t="s">
+      <c r="F160" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="G160" s="1" t="s">
         <v>795</v>
       </c>
     </row>
@@ -9553,19 +9546,19 @@
       <c r="B161" t="s">
         <v>796</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="D161" s="1" t="s">
         <v>798</v>
       </c>
       <c r="E161" t="s">
         <v>1577</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="F161" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="G161" s="2" t="s">
+      <c r="G161" s="1" t="s">
         <v>800</v>
       </c>
     </row>
@@ -9576,19 +9569,19 @@
       <c r="B162" t="s">
         <v>801</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D162" s="1" t="s">
         <v>803</v>
       </c>
       <c r="E162" t="s">
         <v>1610</v>
       </c>
-      <c r="F162" s="3" t="s">
+      <c r="F162" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="G162" s="1" t="s">
         <v>805</v>
       </c>
     </row>
@@ -9599,19 +9592,19 @@
       <c r="B163" t="s">
         <v>806</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="D163" s="1" t="s">
         <v>808</v>
       </c>
       <c r="E163" t="s">
         <v>1611</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="F163" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="G163" s="1" t="s">
         <v>810</v>
       </c>
     </row>
@@ -9622,19 +9615,19 @@
       <c r="B164" t="s">
         <v>811</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="D164" s="2" t="s">
+      <c r="D164" s="1" t="s">
         <v>813</v>
       </c>
       <c r="E164" t="s">
         <v>1612</v>
       </c>
-      <c r="F164" s="3" t="s">
+      <c r="F164" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="G164" s="1" t="s">
         <v>815</v>
       </c>
     </row>
@@ -9645,19 +9638,19 @@
       <c r="B165" t="s">
         <v>816</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="D165" s="2" t="s">
+      <c r="D165" s="1" t="s">
         <v>818</v>
       </c>
       <c r="E165" t="s">
         <v>1613</v>
       </c>
-      <c r="F165" s="3" t="s">
+      <c r="F165" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="G165" s="1" t="s">
         <v>820</v>
       </c>
     </row>
@@ -9668,19 +9661,19 @@
       <c r="B166" t="s">
         <v>821</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="D166" s="1" t="s">
         <v>823</v>
       </c>
       <c r="E166" t="s">
         <v>1614</v>
       </c>
-      <c r="F166" s="3" t="s">
+      <c r="F166" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="G166" s="1" t="s">
         <v>825</v>
       </c>
     </row>
@@ -9691,19 +9684,19 @@
       <c r="B167" t="s">
         <v>826</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D167" s="1" t="s">
         <v>828</v>
       </c>
       <c r="E167" t="s">
         <v>1615</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F167" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="G167" s="1" t="s">
         <v>830</v>
       </c>
     </row>
@@ -9714,19 +9707,19 @@
       <c r="B168" t="s">
         <v>831</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="D168" s="2" t="s">
+      <c r="D168" s="1" t="s">
         <v>833</v>
       </c>
       <c r="E168" t="s">
         <v>1616</v>
       </c>
-      <c r="F168" s="3" t="s">
+      <c r="F168" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="G168" s="2" t="s">
+      <c r="G168" s="1" t="s">
         <v>835</v>
       </c>
     </row>
@@ -9737,19 +9730,19 @@
       <c r="B169" t="s">
         <v>836</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C169" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="D169" s="2" t="s">
+      <c r="D169" s="1" t="s">
         <v>838</v>
       </c>
       <c r="E169" t="s">
         <v>1617</v>
       </c>
-      <c r="F169" s="3" t="s">
+      <c r="F169" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="G169" s="1" t="s">
         <v>840</v>
       </c>
     </row>
@@ -9760,19 +9753,19 @@
       <c r="B170" t="s">
         <v>841</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="C170" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="D170" s="2" t="s">
+      <c r="D170" s="1" t="s">
         <v>843</v>
       </c>
       <c r="E170" t="s">
         <v>1619</v>
       </c>
-      <c r="F170" s="3" t="s">
+      <c r="F170" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="G170" s="2" t="s">
+      <c r="G170" s="1" t="s">
         <v>845</v>
       </c>
     </row>
@@ -9783,19 +9776,19 @@
       <c r="B171" t="s">
         <v>846</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="C171" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="D171" s="2" t="s">
+      <c r="D171" s="1" t="s">
         <v>848</v>
       </c>
       <c r="E171" t="s">
         <v>1620</v>
       </c>
-      <c r="F171" s="3" t="s">
+      <c r="F171" s="2" t="s">
         <v>849</v>
       </c>
-      <c r="G171" s="2" t="s">
+      <c r="G171" s="1" t="s">
         <v>850</v>
       </c>
     </row>
@@ -9806,19 +9799,19 @@
       <c r="B172" t="s">
         <v>851</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="C172" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="D172" s="1" t="s">
         <v>853</v>
       </c>
       <c r="E172" t="s">
         <v>1621</v>
       </c>
-      <c r="F172" s="3" t="s">
+      <c r="F172" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="G172" s="2" t="s">
+      <c r="G172" s="1" t="s">
         <v>855</v>
       </c>
     </row>
@@ -9829,19 +9822,19 @@
       <c r="B173" t="s">
         <v>856</v>
       </c>
-      <c r="C173" s="2" t="s">
+      <c r="C173" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="D173" s="2" t="s">
+      <c r="D173" s="1" t="s">
         <v>858</v>
       </c>
       <c r="E173" t="s">
         <v>1622</v>
       </c>
-      <c r="F173" s="3" t="s">
+      <c r="F173" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="G173" s="2" t="s">
+      <c r="G173" s="1" t="s">
         <v>860</v>
       </c>
     </row>
@@ -9852,19 +9845,19 @@
       <c r="B174" t="s">
         <v>861</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="C174" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="D174" s="1" t="s">
         <v>863</v>
       </c>
       <c r="E174" t="s">
         <v>1623</v>
       </c>
-      <c r="F174" s="3" t="s">
+      <c r="F174" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="G174" s="2" t="s">
+      <c r="G174" s="1" t="s">
         <v>865</v>
       </c>
     </row>
@@ -9875,19 +9868,19 @@
       <c r="B175" t="s">
         <v>866</v>
       </c>
-      <c r="C175" s="2" t="s">
+      <c r="C175" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="D175" s="2" t="s">
+      <c r="D175" s="1" t="s">
         <v>868</v>
       </c>
       <c r="E175" t="s">
         <v>1624</v>
       </c>
-      <c r="F175" s="3" t="s">
+      <c r="F175" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="G175" s="2" t="s">
+      <c r="G175" s="1" t="s">
         <v>870</v>
       </c>
     </row>
@@ -9898,19 +9891,19 @@
       <c r="B176" t="s">
         <v>871</v>
       </c>
-      <c r="C176" s="2" t="s">
+      <c r="C176" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="D176" s="2" t="s">
+      <c r="D176" s="1" t="s">
         <v>873</v>
       </c>
       <c r="E176" t="s">
         <v>1625</v>
       </c>
-      <c r="F176" s="3" t="s">
+      <c r="F176" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="G176" s="2" t="s">
+      <c r="G176" s="1" t="s">
         <v>875</v>
       </c>
     </row>
@@ -9921,19 +9914,19 @@
       <c r="B177" t="s">
         <v>876</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C177" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="D177" s="2" t="s">
+      <c r="D177" s="1" t="s">
         <v>878</v>
       </c>
       <c r="E177" t="s">
         <v>1626</v>
       </c>
-      <c r="F177" s="3" t="s">
+      <c r="F177" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="G177" s="2" t="s">
+      <c r="G177" s="1" t="s">
         <v>880</v>
       </c>
     </row>
@@ -9944,19 +9937,19 @@
       <c r="B178" t="s">
         <v>881</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="C178" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="D178" s="2" t="s">
+      <c r="D178" s="1" t="s">
         <v>883</v>
       </c>
       <c r="E178" t="s">
         <v>1627</v>
       </c>
-      <c r="F178" s="3" t="s">
+      <c r="F178" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="G178" s="2" t="s">
+      <c r="G178" s="1" t="s">
         <v>885</v>
       </c>
     </row>
@@ -9967,19 +9960,19 @@
       <c r="B179" t="s">
         <v>886</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="C179" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="D179" s="2" t="s">
+      <c r="D179" s="1" t="s">
         <v>888</v>
       </c>
       <c r="E179" t="s">
         <v>1628</v>
       </c>
-      <c r="F179" s="3" t="s">
+      <c r="F179" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="G179" s="2" t="s">
+      <c r="G179" s="1" t="s">
         <v>890</v>
       </c>
     </row>
@@ -9990,19 +9983,19 @@
       <c r="B180" t="s">
         <v>891</v>
       </c>
-      <c r="C180" s="2" t="s">
+      <c r="C180" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="D180" s="2" t="s">
+      <c r="D180" s="1" t="s">
         <v>893</v>
       </c>
       <c r="E180" t="s">
         <v>1629</v>
       </c>
-      <c r="F180" s="3" t="s">
+      <c r="F180" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="G180" s="2" t="s">
+      <c r="G180" s="1" t="s">
         <v>895</v>
       </c>
     </row>
@@ -10013,19 +10006,19 @@
       <c r="B181" t="s">
         <v>896</v>
       </c>
-      <c r="C181" s="2" t="s">
+      <c r="C181" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="D181" s="2" t="s">
+      <c r="D181" s="1" t="s">
         <v>898</v>
       </c>
       <c r="E181" t="s">
         <v>1630</v>
       </c>
-      <c r="F181" s="3" t="s">
+      <c r="F181" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="G181" s="2" t="s">
+      <c r="G181" s="1" t="s">
         <v>900</v>
       </c>
     </row>
@@ -10036,19 +10029,19 @@
       <c r="B182" t="s">
         <v>901</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="C182" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="D182" s="2" t="s">
+      <c r="D182" s="1" t="s">
         <v>903</v>
       </c>
       <c r="E182" t="s">
         <v>1631</v>
       </c>
-      <c r="F182" s="3" t="s">
+      <c r="F182" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="G182" s="2" t="s">
+      <c r="G182" s="1" t="s">
         <v>905</v>
       </c>
     </row>
@@ -10059,19 +10052,19 @@
       <c r="B183" t="s">
         <v>906</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="C183" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="D183" s="2" t="s">
+      <c r="D183" s="1" t="s">
         <v>908</v>
       </c>
       <c r="E183" t="s">
         <v>1632</v>
       </c>
-      <c r="F183" s="3" t="s">
+      <c r="F183" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="G183" s="2" t="s">
+      <c r="G183" s="1" t="s">
         <v>910</v>
       </c>
     </row>
@@ -10082,19 +10075,19 @@
       <c r="B184" t="s">
         <v>911</v>
       </c>
-      <c r="C184" s="2" t="s">
+      <c r="C184" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="D184" s="1" t="s">
         <v>913</v>
       </c>
       <c r="E184" t="s">
         <v>1633</v>
       </c>
-      <c r="F184" s="3" t="s">
+      <c r="F184" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="G184" s="2" t="s">
+      <c r="G184" s="1" t="s">
         <v>915</v>
       </c>
     </row>
@@ -10105,19 +10098,19 @@
       <c r="B185" t="s">
         <v>916</v>
       </c>
-      <c r="C185" s="2" t="s">
+      <c r="C185" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="D185" s="1" t="s">
         <v>918</v>
       </c>
       <c r="E185" t="s">
         <v>1634</v>
       </c>
-      <c r="F185" s="3" t="s">
+      <c r="F185" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="G185" s="1" t="s">
         <v>920</v>
       </c>
     </row>
@@ -10128,19 +10121,19 @@
       <c r="B186" t="s">
         <v>921</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="C186" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="D186" s="2" t="s">
+      <c r="D186" s="1" t="s">
         <v>923</v>
       </c>
       <c r="E186" t="s">
         <v>1635</v>
       </c>
-      <c r="F186" s="3" t="s">
+      <c r="F186" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="G186" s="2" t="s">
+      <c r="G186" s="1" t="s">
         <v>925</v>
       </c>
     </row>
@@ -10151,19 +10144,19 @@
       <c r="B187" t="s">
         <v>926</v>
       </c>
-      <c r="C187" s="2" t="s">
+      <c r="C187" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="D187" s="1" t="s">
         <v>928</v>
       </c>
       <c r="E187" t="s">
         <v>1636</v>
       </c>
-      <c r="F187" s="3" t="s">
+      <c r="F187" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="G187" s="2" t="s">
+      <c r="G187" s="1" t="s">
         <v>930</v>
       </c>
     </row>
@@ -10174,19 +10167,19 @@
       <c r="B188" t="s">
         <v>931</v>
       </c>
-      <c r="C188" s="2" t="s">
+      <c r="C188" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="D188" s="2" t="s">
+      <c r="D188" s="1" t="s">
         <v>933</v>
       </c>
       <c r="E188" t="s">
         <v>1637</v>
       </c>
-      <c r="F188" s="3" t="s">
+      <c r="F188" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="G188" s="2" t="s">
+      <c r="G188" s="1" t="s">
         <v>935</v>
       </c>
     </row>
@@ -10197,19 +10190,19 @@
       <c r="B189" t="s">
         <v>936</v>
       </c>
-      <c r="C189" s="2" t="s">
+      <c r="C189" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="D189" s="2" t="s">
+      <c r="D189" s="1" t="s">
         <v>938</v>
       </c>
       <c r="E189" t="s">
         <v>1638</v>
       </c>
-      <c r="F189" s="3" t="s">
+      <c r="F189" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="G189" s="2" t="s">
+      <c r="G189" s="1" t="s">
         <v>940</v>
       </c>
     </row>
@@ -10220,19 +10213,19 @@
       <c r="B190" t="s">
         <v>941</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="C190" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="D190" s="2" t="s">
+      <c r="D190" s="1" t="s">
         <v>943</v>
       </c>
       <c r="E190" t="s">
         <v>1639</v>
       </c>
-      <c r="F190" s="3" t="s">
+      <c r="F190" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="G190" s="2" t="s">
+      <c r="G190" s="1" t="s">
         <v>945</v>
       </c>
     </row>
@@ -10243,19 +10236,19 @@
       <c r="B191" t="s">
         <v>946</v>
       </c>
-      <c r="C191" s="2" t="s">
+      <c r="C191" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="D191" s="2" t="s">
+      <c r="D191" s="1" t="s">
         <v>948</v>
       </c>
       <c r="E191" t="s">
         <v>1640</v>
       </c>
-      <c r="F191" s="3" t="s">
+      <c r="F191" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="G191" s="2" t="s">
+      <c r="G191" s="1" t="s">
         <v>950</v>
       </c>
     </row>
@@ -10266,19 +10259,19 @@
       <c r="B192" t="s">
         <v>951</v>
       </c>
-      <c r="C192" s="2" t="s">
+      <c r="C192" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="D192" s="2" t="s">
+      <c r="D192" s="1" t="s">
         <v>953</v>
       </c>
       <c r="E192" t="s">
         <v>1641</v>
       </c>
-      <c r="F192" s="3" t="s">
+      <c r="F192" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G192" s="2" t="s">
+      <c r="G192" s="1" t="s">
         <v>954</v>
       </c>
     </row>
@@ -10289,19 +10282,19 @@
       <c r="B193" t="s">
         <v>955</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="C193" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="D193" s="2" t="s">
+      <c r="D193" s="1" t="s">
         <v>957</v>
       </c>
       <c r="E193" t="s">
         <v>1642</v>
       </c>
-      <c r="F193" s="3" t="s">
+      <c r="F193" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="G193" s="2" t="s">
+      <c r="G193" s="1" t="s">
         <v>959</v>
       </c>
     </row>
@@ -10312,19 +10305,19 @@
       <c r="B194" t="s">
         <v>960</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="C194" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="D194" s="1" t="s">
         <v>962</v>
       </c>
       <c r="E194" t="s">
         <v>1643</v>
       </c>
-      <c r="F194" s="3" t="s">
+      <c r="F194" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="G194" s="2" t="s">
+      <c r="G194" s="1" t="s">
         <v>964</v>
       </c>
     </row>
@@ -10335,19 +10328,19 @@
       <c r="B195" t="s">
         <v>965</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C195" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="D195" s="1" t="s">
         <v>967</v>
       </c>
       <c r="E195" t="s">
         <v>1644</v>
       </c>
-      <c r="F195" s="3" t="s">
+      <c r="F195" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="G195" s="2" t="s">
+      <c r="G195" s="1" t="s">
         <v>969</v>
       </c>
     </row>
@@ -10358,19 +10351,19 @@
       <c r="B196" t="s">
         <v>970</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="C196" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="D196" s="2" t="s">
+      <c r="D196" s="1" t="s">
         <v>972</v>
       </c>
       <c r="E196" t="s">
         <v>1645</v>
       </c>
-      <c r="F196" s="3" t="s">
+      <c r="F196" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="G196" s="2" t="s">
+      <c r="G196" s="1" t="s">
         <v>974</v>
       </c>
     </row>
@@ -10381,19 +10374,19 @@
       <c r="B197" t="s">
         <v>975</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C197" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="D197" s="2" t="s">
+      <c r="D197" s="1" t="s">
         <v>977</v>
       </c>
       <c r="E197" t="s">
         <v>1646</v>
       </c>
-      <c r="F197" s="3" t="s">
+      <c r="F197" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="G197" s="2" t="s">
+      <c r="G197" s="1" t="s">
         <v>979</v>
       </c>
     </row>
@@ -10404,19 +10397,19 @@
       <c r="B198" t="s">
         <v>980</v>
       </c>
-      <c r="C198" s="2" t="s">
+      <c r="C198" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="D198" s="2" t="s">
+      <c r="D198" s="1" t="s">
         <v>982</v>
       </c>
       <c r="E198" t="s">
         <v>1615</v>
       </c>
-      <c r="F198" s="3" t="s">
+      <c r="F198" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="G198" s="2" t="s">
+      <c r="G198" s="1" t="s">
         <v>984</v>
       </c>
     </row>
@@ -10427,19 +10420,19 @@
       <c r="B199" t="s">
         <v>985</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C199" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D199" s="1" t="s">
         <v>987</v>
       </c>
       <c r="E199" t="s">
         <v>1647</v>
       </c>
-      <c r="F199" s="3" t="s">
+      <c r="F199" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="G199" s="2" t="s">
+      <c r="G199" s="1" t="s">
         <v>989</v>
       </c>
     </row>
@@ -10450,19 +10443,19 @@
       <c r="B200" t="s">
         <v>990</v>
       </c>
-      <c r="C200" s="2" t="s">
+      <c r="C200" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="D200" s="1" t="s">
         <v>992</v>
       </c>
       <c r="E200" t="s">
         <v>1648</v>
       </c>
-      <c r="F200" s="3" t="s">
+      <c r="F200" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="G200" s="2" t="s">
+      <c r="G200" s="1" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10473,19 +10466,19 @@
       <c r="B201" t="s">
         <v>995</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="C201" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="D201" s="2" t="s">
+      <c r="D201" s="1" t="s">
         <v>997</v>
       </c>
       <c r="E201" t="s">
         <v>1649</v>
       </c>
-      <c r="F201" s="3" t="s">
+      <c r="F201" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="G201" s="2" t="s">
+      <c r="G201" s="1" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10496,19 +10489,19 @@
       <c r="B202" t="s">
         <v>1000</v>
       </c>
-      <c r="C202" s="2" t="s">
+      <c r="C202" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="D202" s="1" t="s">
         <v>1002</v>
       </c>
       <c r="E202" t="s">
         <v>1624</v>
       </c>
-      <c r="F202" s="3" t="s">
+      <c r="F202" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="G202" s="1" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10519,19 +10512,19 @@
       <c r="B203" t="s">
         <v>1005</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="C203" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="D203" s="1" t="s">
         <v>1007</v>
       </c>
       <c r="E203" t="s">
         <v>1650</v>
       </c>
-      <c r="F203" s="3" t="s">
+      <c r="F203" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="G203" s="2" t="s">
+      <c r="G203" s="1" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10542,19 +10535,19 @@
       <c r="B204" t="s">
         <v>1010</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="C204" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="D204" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E204" t="s">
         <v>1651</v>
       </c>
-      <c r="F204" s="3" t="s">
+      <c r="F204" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="G204" s="2" t="s">
+      <c r="G204" s="1" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10565,19 +10558,19 @@
       <c r="B205" t="s">
         <v>1015</v>
       </c>
-      <c r="C205" s="2" t="s">
+      <c r="C205" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="D205" s="1" t="s">
         <v>1017</v>
       </c>
       <c r="E205" t="s">
         <v>1652</v>
       </c>
-      <c r="F205" s="3" t="s">
+      <c r="F205" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="G205" s="2" t="s">
+      <c r="G205" s="1" t="s">
         <v>1019</v>
       </c>
     </row>
@@ -10588,19 +10581,19 @@
       <c r="B206" t="s">
         <v>1020</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="C206" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="D206" s="1" t="s">
         <v>1022</v>
       </c>
       <c r="E206" t="s">
         <v>1653</v>
       </c>
-      <c r="F206" s="3" t="s">
+      <c r="F206" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="G206" s="2" t="s">
+      <c r="G206" s="1" t="s">
         <v>1024</v>
       </c>
     </row>
@@ -10611,19 +10604,19 @@
       <c r="B207" t="s">
         <v>1025</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="C207" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="D207" s="2" t="s">
+      <c r="D207" s="1" t="s">
         <v>1027</v>
       </c>
       <c r="E207" t="s">
         <v>1654</v>
       </c>
-      <c r="F207" s="3" t="s">
+      <c r="F207" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="G207" s="2" t="s">
+      <c r="G207" s="1" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -10634,19 +10627,19 @@
       <c r="B208" t="s">
         <v>1030</v>
       </c>
-      <c r="C208" s="2" t="s">
+      <c r="C208" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="D208" s="1" t="s">
         <v>1032</v>
       </c>
       <c r="E208" t="s">
         <v>1531</v>
       </c>
-      <c r="F208" s="3" t="s">
+      <c r="F208" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="G208" s="2" t="s">
+      <c r="G208" s="1" t="s">
         <v>1034</v>
       </c>
     </row>
@@ -10657,19 +10650,19 @@
       <c r="B209" t="s">
         <v>1035</v>
       </c>
-      <c r="C209" s="2" t="s">
+      <c r="C209" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="D209" s="2" t="s">
+      <c r="D209" s="1" t="s">
         <v>1037</v>
       </c>
       <c r="E209" t="s">
         <v>1655</v>
       </c>
-      <c r="F209" s="3" t="s">
+      <c r="F209" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="G209" s="2" t="s">
+      <c r="G209" s="1" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10680,19 +10673,19 @@
       <c r="B210" t="s">
         <v>1040</v>
       </c>
-      <c r="C210" s="2" t="s">
+      <c r="C210" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="D210" s="1" t="s">
         <v>1042</v>
       </c>
       <c r="E210" t="s">
         <v>1656</v>
       </c>
-      <c r="F210" s="3" t="s">
+      <c r="F210" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="G210" s="2" t="s">
+      <c r="G210" s="1" t="s">
         <v>1044</v>
       </c>
     </row>
@@ -10703,19 +10696,19 @@
       <c r="B211" t="s">
         <v>1045</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="C211" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="D211" s="2" t="s">
+      <c r="D211" s="1" t="s">
         <v>1047</v>
       </c>
       <c r="E211" t="s">
         <v>1657</v>
       </c>
-      <c r="F211" s="3" t="s">
+      <c r="F211" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="G211" s="2" t="s">
+      <c r="G211" s="1" t="s">
         <v>1049</v>
       </c>
     </row>
@@ -10726,19 +10719,19 @@
       <c r="B212" t="s">
         <v>1050</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="C212" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="D212" s="2" t="s">
+      <c r="D212" s="1" t="s">
         <v>1052</v>
       </c>
       <c r="E212" t="s">
         <v>1658</v>
       </c>
-      <c r="F212" s="3" t="s">
+      <c r="F212" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="G212" s="2" t="s">
+      <c r="G212" s="1" t="s">
         <v>1054</v>
       </c>
     </row>
@@ -10749,19 +10742,19 @@
       <c r="B213" t="s">
         <v>1055</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="C213" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="D213" s="2" t="s">
+      <c r="D213" s="1" t="s">
         <v>1057</v>
       </c>
       <c r="E213" t="s">
         <v>1654</v>
       </c>
-      <c r="F213" s="3" t="s">
+      <c r="F213" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="G213" s="2" t="s">
+      <c r="G213" s="1" t="s">
         <v>1059</v>
       </c>
     </row>
@@ -10772,19 +10765,19 @@
       <c r="B214" t="s">
         <v>1060</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="C214" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="D214" s="2" t="s">
+      <c r="D214" s="1" t="s">
         <v>1062</v>
       </c>
       <c r="E214" t="s">
         <v>1659</v>
       </c>
-      <c r="F214" s="3" t="s">
+      <c r="F214" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="G214" s="2" t="s">
+      <c r="G214" s="1" t="s">
         <v>1064</v>
       </c>
     </row>
@@ -10795,19 +10788,19 @@
       <c r="B215" t="s">
         <v>1065</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C215" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="D215" s="2" t="s">
+      <c r="D215" s="1" t="s">
         <v>1067</v>
       </c>
       <c r="E215" t="s">
         <v>1660</v>
       </c>
-      <c r="F215" s="3" t="s">
+      <c r="F215" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="G215" s="2" t="s">
+      <c r="G215" s="1" t="s">
         <v>1069</v>
       </c>
     </row>
@@ -10818,19 +10811,19 @@
       <c r="B216" t="s">
         <v>1070</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C216" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="D216" s="1" t="s">
         <v>1072</v>
       </c>
       <c r="E216" t="s">
         <v>1580</v>
       </c>
-      <c r="F216" s="3" t="s">
+      <c r="F216" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="G216" s="2" t="s">
+      <c r="G216" s="1" t="s">
         <v>1074</v>
       </c>
     </row>
@@ -10841,19 +10834,19 @@
       <c r="B217" t="s">
         <v>1075</v>
       </c>
-      <c r="C217" s="2" t="s">
+      <c r="C217" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="D217" s="1" t="s">
         <v>1077</v>
       </c>
       <c r="E217" t="s">
         <v>1661</v>
       </c>
-      <c r="F217" s="3" t="s">
+      <c r="F217" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G217" s="2" t="s">
+      <c r="G217" s="1" t="s">
         <v>1078</v>
       </c>
     </row>
@@ -10864,19 +10857,19 @@
       <c r="B218" t="s">
         <v>1079</v>
       </c>
-      <c r="C218" s="2" t="s">
+      <c r="C218" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="D218" s="2" t="s">
+      <c r="D218" s="1" t="s">
         <v>1081</v>
       </c>
       <c r="E218" t="s">
         <v>1662</v>
       </c>
-      <c r="F218" s="3" t="s">
+      <c r="F218" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="G218" s="2" t="s">
+      <c r="G218" s="1" t="s">
         <v>1083</v>
       </c>
     </row>
@@ -10887,19 +10880,19 @@
       <c r="B219" t="s">
         <v>1084</v>
       </c>
-      <c r="C219" s="2" t="s">
+      <c r="C219" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="D219" s="2" t="s">
+      <c r="D219" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="E219" t="s">
         <v>1663</v>
       </c>
-      <c r="F219" s="3" t="s">
+      <c r="F219" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="G219" s="2" t="s">
+      <c r="G219" s="1" t="s">
         <v>1088</v>
       </c>
     </row>
@@ -10910,19 +10903,19 @@
       <c r="B220" t="s">
         <v>1089</v>
       </c>
-      <c r="C220" s="2" t="s">
+      <c r="C220" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="D220" s="1" t="s">
         <v>1091</v>
       </c>
       <c r="E220" t="s">
         <v>1664</v>
       </c>
-      <c r="F220" s="3" t="s">
+      <c r="F220" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="G220" s="2" t="s">
+      <c r="G220" s="1" t="s">
         <v>1093</v>
       </c>
     </row>
@@ -10933,19 +10926,19 @@
       <c r="B221" t="s">
         <v>1094</v>
       </c>
-      <c r="C221" s="2" t="s">
+      <c r="C221" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="D221" s="1" t="s">
         <v>1096</v>
       </c>
       <c r="E221" t="s">
         <v>1665</v>
       </c>
-      <c r="F221" s="3" t="s">
+      <c r="F221" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="G221" s="2" t="s">
+      <c r="G221" s="1" t="s">
         <v>1098</v>
       </c>
     </row>
@@ -10956,19 +10949,19 @@
       <c r="B222" t="s">
         <v>1099</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C222" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="D222" s="2" t="s">
+      <c r="D222" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="E222" t="s">
         <v>1666</v>
       </c>
-      <c r="F222" s="3" t="s">
+      <c r="F222" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="G222" s="2" t="s">
+      <c r="G222" s="1" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -10979,19 +10972,19 @@
       <c r="B223" t="s">
         <v>1104</v>
       </c>
-      <c r="C223" s="2" t="s">
+      <c r="C223" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="D223" s="1" t="s">
         <v>1106</v>
       </c>
       <c r="E223" t="s">
         <v>1667</v>
       </c>
-      <c r="F223" s="3" t="s">
+      <c r="F223" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="G223" s="2" t="s">
+      <c r="G223" s="1" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -11002,19 +10995,19 @@
       <c r="B224" t="s">
         <v>1109</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="C224" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="D224" s="1" t="s">
         <v>1111</v>
       </c>
       <c r="E224" t="s">
         <v>1668</v>
       </c>
-      <c r="F224" s="3" t="s">
+      <c r="F224" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="G224" s="2" t="s">
+      <c r="G224" s="1" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -11025,19 +11018,19 @@
       <c r="B225" t="s">
         <v>1113</v>
       </c>
-      <c r="C225" s="2" t="s">
+      <c r="C225" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="D225" s="2" t="s">
+      <c r="D225" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E225" t="s">
         <v>1669</v>
       </c>
-      <c r="F225" s="3" t="s">
+      <c r="F225" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="G225" s="2" t="s">
+      <c r="G225" s="1" t="s">
         <v>1117</v>
       </c>
     </row>
@@ -11048,19 +11041,19 @@
       <c r="B226" t="s">
         <v>1118</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="C226" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="D226" s="1" t="s">
         <v>1120</v>
       </c>
       <c r="E226" t="s">
         <v>1670</v>
       </c>
-      <c r="F226" s="3" t="s">
+      <c r="F226" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="G226" s="2" t="s">
+      <c r="G226" s="1" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -11071,19 +11064,19 @@
       <c r="B227" t="s">
         <v>1123</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="C227" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="D227" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E227" t="s">
         <v>1671</v>
       </c>
-      <c r="F227" s="3" t="s">
+      <c r="F227" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="G227" s="2" t="s">
+      <c r="G227" s="1" t="s">
         <v>1126</v>
       </c>
     </row>
@@ -11094,19 +11087,19 @@
       <c r="B228" t="s">
         <v>1127</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="C228" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="D228" s="1" t="s">
         <v>1129</v>
       </c>
       <c r="E228" t="s">
         <v>1672</v>
       </c>
-      <c r="F228" s="3" t="s">
+      <c r="F228" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="G228" s="2" t="s">
+      <c r="G228" s="1" t="s">
         <v>1131</v>
       </c>
     </row>
@@ -11117,19 +11110,19 @@
       <c r="B229" t="s">
         <v>1132</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="C229" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="D229" s="1" t="s">
         <v>1134</v>
       </c>
       <c r="E229" t="s">
         <v>1673</v>
       </c>
-      <c r="F229" s="3" t="s">
+      <c r="F229" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="G229" s="2" t="s">
+      <c r="G229" s="1" t="s">
         <v>1136</v>
       </c>
     </row>
@@ -11140,19 +11133,19 @@
       <c r="B230" t="s">
         <v>1137</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C230" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="D230" s="1" t="s">
         <v>1139</v>
       </c>
       <c r="E230" t="s">
         <v>1674</v>
       </c>
-      <c r="F230" s="3" t="s">
+      <c r="F230" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="G230" s="2" t="s">
+      <c r="G230" s="1" t="s">
         <v>1140</v>
       </c>
     </row>
@@ -11163,19 +11156,19 @@
       <c r="B231" t="s">
         <v>1141</v>
       </c>
-      <c r="C231" s="2" t="s">
+      <c r="C231" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="D231" s="2" t="s">
+      <c r="D231" s="1" t="s">
         <v>1143</v>
       </c>
       <c r="E231" t="s">
         <v>1675</v>
       </c>
-      <c r="F231" s="3" t="s">
+      <c r="F231" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="G231" s="2" t="s">
+      <c r="G231" s="1" t="s">
         <v>1145</v>
       </c>
     </row>
@@ -11186,19 +11179,19 @@
       <c r="B232" t="s">
         <v>1146</v>
       </c>
-      <c r="C232" s="2" t="s">
+      <c r="C232" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="D232" s="1" t="s">
         <v>1148</v>
       </c>
       <c r="E232" t="s">
         <v>1676</v>
       </c>
-      <c r="F232" s="3" t="s">
+      <c r="F232" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="G232" s="2" t="s">
+      <c r="G232" s="1" t="s">
         <v>1150</v>
       </c>
     </row>
@@ -11209,19 +11202,19 @@
       <c r="B233" t="s">
         <v>1151</v>
       </c>
-      <c r="C233" s="2" t="s">
+      <c r="C233" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="D233" s="2" t="s">
+      <c r="D233" s="1" t="s">
         <v>1153</v>
       </c>
       <c r="E233" t="s">
         <v>1677</v>
       </c>
-      <c r="F233" s="3" t="s">
+      <c r="F233" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="G233" s="2" t="s">
+      <c r="G233" s="1" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11232,19 +11225,19 @@
       <c r="B234" t="s">
         <v>1156</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="C234" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="D234" s="1" t="s">
         <v>1158</v>
       </c>
       <c r="E234" t="s">
         <v>1678</v>
       </c>
-      <c r="F234" s="3" t="s">
+      <c r="F234" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="G234" s="2" t="s">
+      <c r="G234" s="1" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11255,19 +11248,19 @@
       <c r="B235" t="s">
         <v>1161</v>
       </c>
-      <c r="C235" s="2" t="s">
+      <c r="C235" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="D235" s="2" t="s">
+      <c r="D235" s="1" t="s">
         <v>1163</v>
       </c>
       <c r="E235" t="s">
         <v>1679</v>
       </c>
-      <c r="F235" s="3" t="s">
+      <c r="F235" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="G235" s="2" t="s">
+      <c r="G235" s="1" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11278,19 +11271,19 @@
       <c r="B236" t="s">
         <v>1168</v>
       </c>
-      <c r="C236" s="2" t="s">
+      <c r="C236" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="D236" s="2" t="s">
+      <c r="D236" s="1" t="s">
         <v>1170</v>
       </c>
       <c r="E236" t="s">
         <v>1680</v>
       </c>
-      <c r="F236" s="3" t="s">
+      <c r="F236" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="G236" s="2" t="s">
+      <c r="G236" s="1" t="s">
         <v>1172</v>
       </c>
     </row>
@@ -11301,19 +11294,19 @@
       <c r="B237" t="s">
         <v>1173</v>
       </c>
-      <c r="C237" s="2" t="s">
+      <c r="C237" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="D237" s="2" t="s">
+      <c r="D237" s="1" t="s">
         <v>1175</v>
       </c>
       <c r="E237" t="s">
         <v>1681</v>
       </c>
-      <c r="F237" s="3" t="s">
+      <c r="F237" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="G237" s="2" t="s">
+      <c r="G237" s="1" t="s">
         <v>1177</v>
       </c>
     </row>
@@ -11324,19 +11317,19 @@
       <c r="B238" t="s">
         <v>1178</v>
       </c>
-      <c r="C238" s="2" t="s">
+      <c r="C238" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="D238" s="1" t="s">
         <v>1180</v>
       </c>
       <c r="E238" t="s">
         <v>1572</v>
       </c>
-      <c r="F238" s="3" t="s">
+      <c r="F238" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="G238" s="2" t="s">
+      <c r="G238" s="1" t="s">
         <v>1182</v>
       </c>
     </row>
@@ -11347,19 +11340,19 @@
       <c r="B239" t="s">
         <v>1183</v>
       </c>
-      <c r="C239" s="2" t="s">
+      <c r="C239" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="D239" s="2" t="s">
+      <c r="D239" s="1" t="s">
         <v>1185</v>
       </c>
       <c r="E239" t="s">
         <v>1580</v>
       </c>
-      <c r="F239" s="3" t="s">
+      <c r="F239" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="G239" s="2" t="s">
+      <c r="G239" s="1" t="s">
         <v>1187</v>
       </c>
     </row>
@@ -11370,19 +11363,19 @@
       <c r="B240" t="s">
         <v>1188</v>
       </c>
-      <c r="C240" s="2" t="s">
+      <c r="C240" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="D240" s="2" t="s">
+      <c r="D240" s="1" t="s">
         <v>1190</v>
       </c>
       <c r="E240" t="s">
         <v>1682</v>
       </c>
-      <c r="F240" s="3" t="s">
+      <c r="F240" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="G240" s="2" t="s">
+      <c r="G240" s="1" t="s">
         <v>1192</v>
       </c>
     </row>
@@ -11393,19 +11386,19 @@
       <c r="B241" t="s">
         <v>1193</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="C241" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="D241" s="2" t="s">
+      <c r="D241" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E241" t="s">
         <v>1683</v>
       </c>
-      <c r="F241" s="3" t="s">
+      <c r="F241" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="G241" s="2" t="s">
+      <c r="G241" s="1" t="s">
         <v>1196</v>
       </c>
     </row>
@@ -11416,19 +11409,19 @@
       <c r="B242" t="s">
         <v>1197</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C242" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="D242" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E242" t="s">
         <v>1684</v>
       </c>
-      <c r="F242" s="3" t="s">
+      <c r="F242" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G242" s="1" t="s">
         <v>1201</v>
       </c>
     </row>
@@ -11439,19 +11432,19 @@
       <c r="B243" t="s">
         <v>1202</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="C243" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="D243" s="2" t="s">
+      <c r="D243" s="1" t="s">
         <v>1204</v>
       </c>
       <c r="E243" t="s">
         <v>1547</v>
       </c>
-      <c r="F243" s="3" t="s">
+      <c r="F243" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="G243" s="2" t="s">
+      <c r="G243" s="1" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -11462,19 +11455,19 @@
       <c r="B244" t="s">
         <v>1207</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C244" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="D244" s="2" t="s">
+      <c r="D244" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="E244" t="s">
         <v>1685</v>
       </c>
-      <c r="F244" s="3" t="s">
+      <c r="F244" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="G244" s="2" t="s">
+      <c r="G244" s="1" t="s">
         <v>1211</v>
       </c>
     </row>
@@ -11485,19 +11478,19 @@
       <c r="B245" t="s">
         <v>1212</v>
       </c>
-      <c r="C245" s="2" t="s">
+      <c r="C245" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="D245" s="2" t="s">
+      <c r="D245" s="1" t="s">
         <v>1214</v>
       </c>
       <c r="E245" t="s">
         <v>1686</v>
       </c>
-      <c r="F245" s="3" t="s">
+      <c r="F245" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="G245" s="2" t="s">
+      <c r="G245" s="1" t="s">
         <v>1216</v>
       </c>
     </row>
@@ -11508,19 +11501,19 @@
       <c r="B246" t="s">
         <v>1217</v>
       </c>
-      <c r="C246" s="2" t="s">
+      <c r="C246" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="D246" s="2" t="s">
+      <c r="D246" s="1" t="s">
         <v>1219</v>
       </c>
       <c r="E246" t="s">
         <v>1687</v>
       </c>
-      <c r="F246" s="3" t="s">
+      <c r="F246" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="G246" s="2" t="s">
+      <c r="G246" s="1" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -11531,19 +11524,19 @@
       <c r="B247" t="s">
         <v>1222</v>
       </c>
-      <c r="C247" s="2" t="s">
+      <c r="C247" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="D247" s="2" t="s">
+      <c r="D247" s="1" t="s">
         <v>1224</v>
       </c>
       <c r="E247" t="s">
         <v>1688</v>
       </c>
-      <c r="F247" s="3" t="s">
+      <c r="F247" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="G247" s="2" t="s">
+      <c r="G247" s="1" t="s">
         <v>1226</v>
       </c>
     </row>
@@ -11554,19 +11547,19 @@
       <c r="B248" t="s">
         <v>1227</v>
       </c>
-      <c r="C248" s="2" t="s">
+      <c r="C248" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="D248" s="2" t="s">
+      <c r="D248" s="1" t="s">
         <v>1229</v>
       </c>
       <c r="E248" t="s">
         <v>1689</v>
       </c>
-      <c r="F248" s="3" t="s">
+      <c r="F248" s="2" t="s">
         <v>1230</v>
       </c>
-      <c r="G248" s="2" t="s">
+      <c r="G248" s="1" t="s">
         <v>1231</v>
       </c>
     </row>
@@ -11577,19 +11570,19 @@
       <c r="B249" t="s">
         <v>1232</v>
       </c>
-      <c r="C249" s="2" t="s">
+      <c r="C249" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="D249" s="1" t="s">
         <v>731</v>
       </c>
       <c r="E249" t="s">
         <v>1690</v>
       </c>
-      <c r="F249" s="3" t="s">
+      <c r="F249" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="G249" s="2" t="s">
+      <c r="G249" s="1" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -11600,19 +11593,19 @@
       <c r="B250" t="s">
         <v>1236</v>
       </c>
-      <c r="C250" s="2" t="s">
+      <c r="C250" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="D250" s="2" t="s">
+      <c r="D250" s="1" t="s">
         <v>1238</v>
       </c>
       <c r="E250" t="s">
         <v>1691</v>
       </c>
-      <c r="F250" s="3" t="s">
+      <c r="F250" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G250" s="2" t="s">
+      <c r="G250" s="1" t="s">
         <v>1239</v>
       </c>
     </row>
@@ -11623,19 +11616,19 @@
       <c r="B251" t="s">
         <v>1240</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="C251" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="D251" s="1" t="s">
         <v>1242</v>
       </c>
       <c r="E251" t="s">
         <v>1692</v>
       </c>
-      <c r="F251" s="3" t="s">
+      <c r="F251" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="G251" s="2" t="s">
+      <c r="G251" s="1" t="s">
         <v>1244</v>
       </c>
     </row>
@@ -11646,19 +11639,19 @@
       <c r="B252" t="s">
         <v>1245</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="C252" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="D252" s="1" t="s">
         <v>1247</v>
       </c>
       <c r="E252" t="s">
         <v>1693</v>
       </c>
-      <c r="F252" s="3" t="s">
+      <c r="F252" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="G252" s="2" t="s">
+      <c r="G252" s="1" t="s">
         <v>1249</v>
       </c>
     </row>
@@ -11669,19 +11662,19 @@
       <c r="B253" t="s">
         <v>1250</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="C253" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="D253" s="2" t="s">
+      <c r="D253" s="1" t="s">
         <v>1252</v>
       </c>
       <c r="E253" t="s">
         <v>1694</v>
       </c>
-      <c r="F253" s="3" t="s">
+      <c r="F253" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="G253" s="2" t="s">
+      <c r="G253" s="1" t="s">
         <v>1254</v>
       </c>
     </row>
@@ -11692,19 +11685,19 @@
       <c r="B254" t="s">
         <v>1255</v>
       </c>
-      <c r="C254" s="2" t="s">
+      <c r="C254" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="D254" s="2" t="s">
+      <c r="D254" s="1" t="s">
         <v>1257</v>
       </c>
       <c r="E254" t="s">
         <v>1695</v>
       </c>
-      <c r="F254" s="3" t="s">
+      <c r="F254" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="G254" s="2" t="s">
+      <c r="G254" s="1" t="s">
         <v>1259</v>
       </c>
     </row>
@@ -11715,19 +11708,19 @@
       <c r="B255" t="s">
         <v>1260</v>
       </c>
-      <c r="C255" s="2" t="s">
+      <c r="C255" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="D255" s="2" t="s">
+      <c r="D255" s="1" t="s">
         <v>1262</v>
       </c>
       <c r="E255" t="s">
         <v>1696</v>
       </c>
-      <c r="F255" s="3" t="s">
+      <c r="F255" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="G255" s="2" t="s">
+      <c r="G255" s="1" t="s">
         <v>1264</v>
       </c>
     </row>
@@ -11738,19 +11731,19 @@
       <c r="B256" t="s">
         <v>1265</v>
       </c>
-      <c r="C256" s="2" t="s">
+      <c r="C256" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="D256" s="2" t="s">
+      <c r="D256" s="1" t="s">
         <v>1267</v>
       </c>
       <c r="E256" t="s">
         <v>1697</v>
       </c>
-      <c r="F256" s="3" t="s">
+      <c r="F256" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G256" s="2" t="s">
+      <c r="G256" s="1" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -11761,19 +11754,19 @@
       <c r="B257" t="s">
         <v>1269</v>
       </c>
-      <c r="C257" s="2" t="s">
+      <c r="C257" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D257" s="2" t="s">
+      <c r="D257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E257" t="s">
         <v>1698</v>
       </c>
-      <c r="F257" s="3" t="s">
+      <c r="F257" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="G257" s="2" t="s">
+      <c r="G257" s="1" t="s">
         <v>1272</v>
       </c>
     </row>
@@ -11784,19 +11777,19 @@
       <c r="B258" t="s">
         <v>1273</v>
       </c>
-      <c r="C258" s="2" t="s">
+      <c r="C258" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="D258" s="2" t="s">
+      <c r="D258" s="1" t="s">
         <v>1275</v>
       </c>
       <c r="E258" t="s">
         <v>1699</v>
       </c>
-      <c r="F258" s="3" t="s">
+      <c r="F258" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="G258" s="2" t="s">
+      <c r="G258" s="1" t="s">
         <v>1276</v>
       </c>
     </row>
@@ -11807,19 +11800,19 @@
       <c r="B259" t="s">
         <v>1277</v>
       </c>
-      <c r="C259" s="2" t="s">
+      <c r="C259" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="D259" s="2" t="s">
+      <c r="D259" s="1" t="s">
         <v>1279</v>
       </c>
       <c r="E259" t="s">
         <v>1700</v>
       </c>
-      <c r="F259" s="3" t="s">
+      <c r="F259" s="2" t="s">
         <v>1280</v>
       </c>
-      <c r="G259" s="2" t="s">
+      <c r="G259" s="1" t="s">
         <v>1281</v>
       </c>
     </row>
@@ -11830,19 +11823,19 @@
       <c r="B260" t="s">
         <v>1282</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="C260" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="D260" s="2" t="s">
+      <c r="D260" s="1" t="s">
         <v>1284</v>
       </c>
       <c r="E260" t="s">
         <v>1701</v>
       </c>
-      <c r="F260" s="3" t="s">
+      <c r="F260" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="G260" s="2" t="s">
+      <c r="G260" s="1" t="s">
         <v>1286</v>
       </c>
     </row>
@@ -11853,19 +11846,19 @@
       <c r="B261" t="s">
         <v>1287</v>
       </c>
-      <c r="C261" s="2" t="s">
+      <c r="C261" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="D261" s="2" t="s">
+      <c r="D261" s="1" t="s">
         <v>1289</v>
       </c>
       <c r="E261" t="s">
         <v>1702</v>
       </c>
-      <c r="F261" s="3" t="s">
+      <c r="F261" s="2" t="s">
         <v>1290</v>
       </c>
-      <c r="G261" s="2" t="s">
+      <c r="G261" s="1" t="s">
         <v>1291</v>
       </c>
     </row>
@@ -11876,19 +11869,19 @@
       <c r="B262" t="s">
         <v>1292</v>
       </c>
-      <c r="C262" s="2" t="s">
+      <c r="C262" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="D262" s="2" t="s">
+      <c r="D262" s="1" t="s">
         <v>1294</v>
       </c>
       <c r="E262" t="s">
         <v>1703</v>
       </c>
-      <c r="F262" s="3" t="s">
+      <c r="F262" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="G262" s="2" t="s">
+      <c r="G262" s="1" t="s">
         <v>1296</v>
       </c>
     </row>
@@ -11899,19 +11892,19 @@
       <c r="B263" t="s">
         <v>1297</v>
       </c>
-      <c r="C263" s="2" t="s">
+      <c r="C263" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="D263" s="2" t="s">
+      <c r="D263" s="1" t="s">
         <v>1299</v>
       </c>
       <c r="E263" t="s">
         <v>1704</v>
       </c>
-      <c r="F263" s="3" t="s">
+      <c r="F263" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="G263" s="2" t="s">
+      <c r="G263" s="1" t="s">
         <v>1301</v>
       </c>
     </row>
@@ -11922,19 +11915,19 @@
       <c r="B264" t="s">
         <v>1302</v>
       </c>
-      <c r="C264" s="2" t="s">
+      <c r="C264" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="D264" s="2" t="s">
+      <c r="D264" s="1" t="s">
         <v>1304</v>
       </c>
       <c r="E264" t="s">
         <v>1705</v>
       </c>
-      <c r="F264" s="3" t="s">
+      <c r="F264" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="G264" s="2" t="s">
+      <c r="G264" s="1" t="s">
         <v>1306</v>
       </c>
     </row>
@@ -11945,19 +11938,19 @@
       <c r="B265" t="s">
         <v>1307</v>
       </c>
-      <c r="C265" s="2" t="s">
+      <c r="C265" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="D265" s="2" t="s">
+      <c r="D265" s="1" t="s">
         <v>1309</v>
       </c>
       <c r="E265" t="s">
         <v>1706</v>
       </c>
-      <c r="F265" s="3" t="s">
+      <c r="F265" s="2" t="s">
         <v>1310</v>
       </c>
-      <c r="G265" s="2" t="s">
+      <c r="G265" s="1" t="s">
         <v>1311</v>
       </c>
     </row>
@@ -11968,19 +11961,19 @@
       <c r="B266" t="s">
         <v>1313</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="C266" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="D266" s="2" t="s">
+      <c r="D266" s="1" t="s">
         <v>1315</v>
       </c>
       <c r="E266" t="s">
         <v>1707</v>
       </c>
-      <c r="F266" s="3" t="s">
+      <c r="F266" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="G266" s="2" t="s">
+      <c r="G266" s="1" t="s">
         <v>1317</v>
       </c>
     </row>
@@ -11991,19 +11984,19 @@
       <c r="B267" t="s">
         <v>1318</v>
       </c>
-      <c r="C267" s="2" t="s">
+      <c r="C267" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="D267" s="2" t="s">
+      <c r="D267" s="1" t="s">
         <v>1319</v>
       </c>
       <c r="E267" t="s">
         <v>1724</v>
       </c>
-      <c r="F267" s="3" t="s">
+      <c r="F267" s="2" t="s">
         <v>1320</v>
       </c>
-      <c r="G267" s="2" t="s">
+      <c r="G267" s="1" t="s">
         <v>1465</v>
       </c>
     </row>
@@ -12014,19 +12007,19 @@
       <c r="B268" t="s">
         <v>1321</v>
       </c>
-      <c r="C268" s="2" t="s">
+      <c r="C268" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="D268" s="2" t="s">
+      <c r="D268" s="1" t="s">
         <v>1323</v>
       </c>
       <c r="E268" t="s">
         <v>1725</v>
       </c>
-      <c r="F268" s="3" t="s">
+      <c r="F268" s="2" t="s">
         <v>1324</v>
       </c>
-      <c r="G268" s="2" t="s">
+      <c r="G268" s="1" t="s">
         <v>1325</v>
       </c>
     </row>
@@ -12037,19 +12030,19 @@
       <c r="B269" t="s">
         <v>1326</v>
       </c>
-      <c r="C269" s="2" t="s">
+      <c r="C269" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="D269" s="2" t="s">
+      <c r="D269" s="1" t="s">
         <v>1295</v>
       </c>
       <c r="E269" t="s">
         <v>1708</v>
       </c>
-      <c r="F269" s="3" t="s">
+      <c r="F269" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G269" s="2" t="s">
+      <c r="G269" s="1" t="s">
         <v>1328</v>
       </c>
     </row>
@@ -12060,19 +12053,19 @@
       <c r="B270" t="s">
         <v>1329</v>
       </c>
-      <c r="C270" s="2" t="s">
+      <c r="C270" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="D270" s="2" t="s">
+      <c r="D270" s="1" t="s">
         <v>1331</v>
       </c>
       <c r="E270" t="s">
         <v>1587</v>
       </c>
-      <c r="F270" s="3" t="s">
+      <c r="F270" s="2" t="s">
         <v>1332</v>
       </c>
-      <c r="G270" s="2" t="s">
+      <c r="G270" s="1" t="s">
         <v>1333</v>
       </c>
     </row>
@@ -12083,19 +12076,19 @@
       <c r="B271" t="s">
         <v>1334</v>
       </c>
-      <c r="C271" s="2" t="s">
+      <c r="C271" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="D271" s="2" t="s">
+      <c r="D271" s="1" t="s">
         <v>1336</v>
       </c>
       <c r="E271" t="s">
         <v>1709</v>
       </c>
-      <c r="F271" s="3" t="s">
+      <c r="F271" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="G271" s="2" t="s">
+      <c r="G271" s="1" t="s">
         <v>1338</v>
       </c>
       <c r="L271" t="s">
@@ -12109,19 +12102,19 @@
       <c r="B272" t="s">
         <v>1339</v>
       </c>
-      <c r="C272" s="2" t="s">
+      <c r="C272" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="D272" s="2" t="s">
+      <c r="D272" s="1" t="s">
         <v>1341</v>
       </c>
       <c r="E272" t="s">
         <v>1710</v>
       </c>
-      <c r="F272" s="3" t="s">
+      <c r="F272" s="2" t="s">
         <v>1342</v>
       </c>
-      <c r="G272" s="2" t="s">
+      <c r="G272" s="1" t="s">
         <v>1343</v>
       </c>
     </row>
@@ -12132,19 +12125,19 @@
       <c r="B273" t="s">
         <v>1344</v>
       </c>
-      <c r="C273" s="2" t="s">
+      <c r="C273" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="D273" s="2" t="s">
+      <c r="D273" s="1" t="s">
         <v>1346</v>
       </c>
       <c r="E273" t="s">
         <v>1711</v>
       </c>
-      <c r="F273" s="3" t="s">
+      <c r="F273" s="2" t="s">
         <v>1347</v>
       </c>
-      <c r="G273" s="2" t="s">
+      <c r="G273" s="1" t="s">
         <v>1348</v>
       </c>
     </row>
@@ -12155,19 +12148,19 @@
       <c r="B274" t="s">
         <v>1349</v>
       </c>
-      <c r="C274" s="2" t="s">
+      <c r="C274" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="D274" s="2" t="s">
+      <c r="D274" s="1" t="s">
         <v>1351</v>
       </c>
       <c r="E274" t="s">
         <v>1712</v>
       </c>
-      <c r="F274" s="3" t="s">
+      <c r="F274" s="2" t="s">
         <v>1352</v>
       </c>
-      <c r="G274" s="2" t="s">
+      <c r="G274" s="1" t="s">
         <v>1353</v>
       </c>
     </row>
@@ -12178,19 +12171,19 @@
       <c r="B275" t="s">
         <v>1354</v>
       </c>
-      <c r="C275" s="2" t="s">
+      <c r="C275" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="D275" s="2" t="s">
+      <c r="D275" s="1" t="s">
         <v>1356</v>
       </c>
       <c r="E275" t="s">
         <v>1713</v>
       </c>
-      <c r="F275" s="3" t="s">
+      <c r="F275" s="2" t="s">
         <v>1357</v>
       </c>
-      <c r="G275" s="2" t="s">
+      <c r="G275" s="1" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -12201,19 +12194,19 @@
       <c r="B276" t="s">
         <v>1359</v>
       </c>
-      <c r="C276" s="2" t="s">
+      <c r="C276" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="D276" s="2" t="s">
+      <c r="D276" s="1" t="s">
         <v>1361</v>
       </c>
       <c r="E276" t="s">
         <v>1554</v>
       </c>
-      <c r="F276" s="3" t="s">
+      <c r="F276" s="2" t="s">
         <v>1362</v>
       </c>
-      <c r="G276" s="2" t="s">
+      <c r="G276" s="1" t="s">
         <v>1363</v>
       </c>
     </row>
@@ -12224,19 +12217,19 @@
       <c r="B277" t="s">
         <v>1364</v>
       </c>
-      <c r="C277" s="2" t="s">
+      <c r="C277" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="D277" s="2" t="s">
+      <c r="D277" s="1" t="s">
         <v>1366</v>
       </c>
       <c r="E277" t="s">
         <v>1658</v>
       </c>
-      <c r="F277" s="3" t="s">
+      <c r="F277" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="G277" s="2" t="s">
+      <c r="G277" s="1" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -12244,19 +12237,19 @@
       <c r="B278" t="s">
         <v>1369</v>
       </c>
-      <c r="C278" s="2" t="s">
+      <c r="C278" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="D278" s="2" t="s">
+      <c r="D278" s="1" t="s">
         <v>1371</v>
       </c>
       <c r="E278" t="s">
         <v>1714</v>
       </c>
-      <c r="F278" s="3" t="s">
+      <c r="F278" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="G278" s="2" t="s">
+      <c r="G278" s="1" t="s">
         <v>1372</v>
       </c>
     </row>
@@ -12267,19 +12260,19 @@
       <c r="B279" t="s">
         <v>1373</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="C279" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="D279" s="2" t="s">
+      <c r="D279" s="1" t="s">
         <v>1375</v>
       </c>
       <c r="E279" t="s">
         <v>1545</v>
       </c>
-      <c r="F279" s="3" t="s">
+      <c r="F279" s="2" t="s">
         <v>1376</v>
       </c>
-      <c r="G279" s="2" t="s">
+      <c r="G279" s="1" t="s">
         <v>1377</v>
       </c>
     </row>
@@ -12290,19 +12283,19 @@
       <c r="B280" t="s">
         <v>1378</v>
       </c>
-      <c r="C280" s="2" t="s">
+      <c r="C280" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="D280" s="2" t="s">
+      <c r="D280" s="1" t="s">
         <v>1380</v>
       </c>
       <c r="E280" t="s">
         <v>1545</v>
       </c>
-      <c r="F280" s="3" t="s">
+      <c r="F280" s="2" t="s">
         <v>1381</v>
       </c>
-      <c r="G280" s="2" t="s">
+      <c r="G280" s="1" t="s">
         <v>1382</v>
       </c>
     </row>
@@ -12313,19 +12306,19 @@
       <c r="B281" t="s">
         <v>1383</v>
       </c>
-      <c r="C281" s="2" t="s">
+      <c r="C281" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="D281" s="2" t="s">
+      <c r="D281" s="1" t="s">
         <v>1385</v>
       </c>
       <c r="E281" t="s">
         <v>1715</v>
       </c>
-      <c r="F281" s="3" t="s">
+      <c r="F281" s="2" t="s">
         <v>1386</v>
       </c>
-      <c r="G281" s="2" t="s">
+      <c r="G281" s="1" t="s">
         <v>1387</v>
       </c>
     </row>
@@ -12336,19 +12329,19 @@
       <c r="B282" t="s">
         <v>1388</v>
       </c>
-      <c r="C282" s="2" t="s">
+      <c r="C282" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="D282" s="2" t="s">
+      <c r="D282" s="1" t="s">
         <v>1390</v>
       </c>
       <c r="E282" t="s">
         <v>1559</v>
       </c>
-      <c r="F282" s="3" t="s">
+      <c r="F282" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="G282" s="2" t="s">
+      <c r="G282" s="1" t="s">
         <v>1392</v>
       </c>
     </row>
@@ -12359,19 +12352,19 @@
       <c r="B283" t="s">
         <v>1393</v>
       </c>
-      <c r="C283" s="2" t="s">
+      <c r="C283" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="D283" s="2" t="s">
+      <c r="D283" s="1" t="s">
         <v>1395</v>
       </c>
       <c r="E283" t="s">
         <v>1543</v>
       </c>
-      <c r="F283" s="3" t="s">
+      <c r="F283" s="2" t="s">
         <v>1396</v>
       </c>
-      <c r="G283" s="2" t="s">
+      <c r="G283" s="1" t="s">
         <v>1397</v>
       </c>
     </row>
@@ -12382,19 +12375,19 @@
       <c r="B284" t="s">
         <v>1398</v>
       </c>
-      <c r="C284" s="2" t="s">
+      <c r="C284" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="D284" s="2" t="s">
+      <c r="D284" s="1" t="s">
         <v>1400</v>
       </c>
       <c r="E284" t="s">
         <v>1582</v>
       </c>
-      <c r="F284" s="3" t="s">
+      <c r="F284" s="2" t="s">
         <v>1401</v>
       </c>
-      <c r="G284" s="2" t="s">
+      <c r="G284" s="1" t="s">
         <v>1402</v>
       </c>
     </row>
@@ -12405,19 +12398,19 @@
       <c r="B285" t="s">
         <v>1403</v>
       </c>
-      <c r="C285" s="2" t="s">
+      <c r="C285" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="D285" s="2" t="s">
+      <c r="D285" s="1" t="s">
         <v>1405</v>
       </c>
       <c r="E285" t="s">
         <v>1716</v>
       </c>
-      <c r="F285" s="3" t="s">
+      <c r="F285" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="G285" s="2" t="s">
+      <c r="G285" s="1" t="s">
         <v>1407</v>
       </c>
     </row>
@@ -12428,19 +12421,19 @@
       <c r="B286" t="s">
         <v>1408</v>
       </c>
-      <c r="C286" s="2" t="s">
+      <c r="C286" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="D286" s="2" t="s">
+      <c r="D286" s="1" t="s">
         <v>1410</v>
       </c>
       <c r="E286" t="s">
         <v>1717</v>
       </c>
-      <c r="F286" s="3" t="s">
+      <c r="F286" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G286" s="2" t="s">
+      <c r="G286" s="1" t="s">
         <v>1411</v>
       </c>
     </row>
@@ -12448,19 +12441,19 @@
       <c r="B287" t="s">
         <v>1412</v>
       </c>
-      <c r="C287" s="2" t="s">
+      <c r="C287" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="D287" s="2" t="s">
+      <c r="D287" s="1" t="s">
         <v>1414</v>
       </c>
       <c r="E287" t="s">
         <v>1718</v>
       </c>
-      <c r="F287" s="3" t="s">
+      <c r="F287" s="2" t="s">
         <v>1415</v>
       </c>
-      <c r="G287" s="2" t="s">
+      <c r="G287" s="1" t="s">
         <v>1416</v>
       </c>
     </row>
@@ -12471,19 +12464,19 @@
       <c r="B288" t="s">
         <v>1417</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="C288" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="D288" s="2" t="s">
+      <c r="D288" s="1" t="s">
         <v>1419</v>
       </c>
       <c r="E288" t="s">
         <v>1719</v>
       </c>
-      <c r="F288" s="3" t="s">
+      <c r="F288" s="2" t="s">
         <v>1420</v>
       </c>
-      <c r="G288" s="2" t="s">
+      <c r="G288" s="1" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -12494,19 +12487,19 @@
       <c r="B289" t="s">
         <v>1166</v>
       </c>
-      <c r="C289" s="2" t="s">
+      <c r="C289" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="D289" s="2" t="s">
+      <c r="D289" s="1" t="s">
         <v>1167</v>
       </c>
       <c r="E289" t="s">
         <v>1720</v>
       </c>
-      <c r="F289" s="3" t="s">
+      <c r="F289" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="G289" s="2" t="s">
+      <c r="G289" s="1" t="s">
         <v>1424</v>
       </c>
     </row>
@@ -12517,19 +12510,19 @@
       <c r="B290" t="s">
         <v>1425</v>
       </c>
-      <c r="C290" s="2" t="s">
+      <c r="C290" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="D290" s="2" t="s">
+      <c r="D290" s="1" t="s">
         <v>1427</v>
       </c>
       <c r="E290" t="s">
         <v>1566</v>
       </c>
-      <c r="F290" s="3" t="s">
+      <c r="F290" s="2" t="s">
         <v>1428</v>
       </c>
-      <c r="G290" s="2" t="s">
+      <c r="G290" s="1" t="s">
         <v>1429</v>
       </c>
     </row>
@@ -12540,19 +12533,19 @@
       <c r="B291" t="s">
         <v>1430</v>
       </c>
-      <c r="C291" s="2" t="s">
+      <c r="C291" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="D291" s="2" t="s">
+      <c r="D291" s="1" t="s">
         <v>1432</v>
       </c>
       <c r="E291" t="s">
         <v>1721</v>
       </c>
-      <c r="F291" s="3" t="s">
+      <c r="F291" s="2" t="s">
         <v>1433</v>
       </c>
-      <c r="G291" s="2" t="s">
+      <c r="G291" s="1" t="s">
         <v>1434</v>
       </c>
     </row>
@@ -12563,19 +12556,19 @@
       <c r="B292" t="s">
         <v>1435</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C292" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="D292" s="1" t="s">
         <v>1437</v>
       </c>
       <c r="E292" t="s">
         <v>1587</v>
       </c>
-      <c r="F292" s="3" t="s">
+      <c r="F292" s="2" t="s">
         <v>1438</v>
       </c>
-      <c r="G292" s="2" t="s">
+      <c r="G292" s="1" t="s">
         <v>1439</v>
       </c>
     </row>
@@ -12586,19 +12579,19 @@
       <c r="B293" t="s">
         <v>1260</v>
       </c>
-      <c r="C293" s="2" t="s">
+      <c r="C293" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="D293" s="2" t="s">
+      <c r="D293" s="1" t="s">
         <v>1441</v>
       </c>
       <c r="E293" t="s">
         <v>1722</v>
       </c>
-      <c r="F293" s="3" t="s">
+      <c r="F293" s="2" t="s">
         <v>1442</v>
       </c>
-      <c r="G293" s="2" t="s">
+      <c r="G293" s="1" t="s">
         <v>1443</v>
       </c>
     </row>
@@ -12609,19 +12602,19 @@
       <c r="B294" t="s">
         <v>1444</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="C294" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="D294" s="2" t="s">
+      <c r="D294" s="1" t="s">
         <v>1077</v>
       </c>
       <c r="E294" t="s">
         <v>1664</v>
       </c>
-      <c r="F294" s="3" t="s">
+      <c r="F294" s="2" t="s">
         <v>1446</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="G294" s="1" t="s">
         <v>1463</v>
       </c>
     </row>
@@ -12632,19 +12625,19 @@
       <c r="B295" t="s">
         <v>1197</v>
       </c>
-      <c r="C295" s="2" t="s">
+      <c r="C295" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="D295" s="2" t="s">
+      <c r="D295" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="E295" t="s">
         <v>1684</v>
       </c>
-      <c r="F295" s="3" t="s">
+      <c r="F295" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="G295" s="2" t="s">
+      <c r="G295" s="1" t="s">
         <v>1201</v>
       </c>
     </row>
@@ -12655,19 +12648,19 @@
       <c r="B296" t="s">
         <v>1202</v>
       </c>
-      <c r="C296" s="2" t="s">
+      <c r="C296" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="D296" s="2" t="s">
+      <c r="D296" s="1" t="s">
         <v>1204</v>
       </c>
       <c r="E296" t="s">
         <v>1547</v>
       </c>
-      <c r="F296" s="3" t="s">
+      <c r="F296" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="G296" s="2" t="s">
+      <c r="G296" s="1" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -12678,19 +12671,19 @@
       <c r="B297" t="s">
         <v>1207</v>
       </c>
-      <c r="C297" s="2" t="s">
+      <c r="C297" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="D297" s="2" t="s">
+      <c r="D297" s="1" t="s">
         <v>1209</v>
       </c>
       <c r="E297" t="s">
         <v>1708</v>
       </c>
-      <c r="F297" s="3" t="s">
+      <c r="F297" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="G297" s="2" t="s">
+      <c r="G297" s="1" t="s">
         <v>1211</v>
       </c>
     </row>
@@ -12701,19 +12694,19 @@
       <c r="B298" t="s">
         <v>1212</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="C298" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="D298" s="2" t="s">
+      <c r="D298" s="1" t="s">
         <v>1214</v>
       </c>
       <c r="E298" t="s">
         <v>1723</v>
       </c>
-      <c r="F298" s="3" t="s">
+      <c r="F298" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="G298" s="2" t="s">
+      <c r="G298" s="1" t="s">
         <v>1216</v>
       </c>
     </row>

--- a/public/data/‏‏Russian_Daily_Word.xlsx
+++ b/public/data/‏‏Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D65433-CEF9-4233-B486-5ED5592096C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348E57C6-9D3E-4A80-97AF-160B2084287A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5534,7 +5534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -5542,9 +5542,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5859,8 +5858,8 @@
     <col min="7" max="7" width="84.58203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
